--- a/model/Outputs/11. Interest rate/30/Output Files/0.1/Output_39_42.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.1/Output_39_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3649836.175042232</v>
+        <v>3650452.18284784</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13249728.69968976</v>
+        <v>13249728.69968975</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13249728.69968976</v>
+        <v>13249728.69968975</v>
       </c>
     </row>
     <row r="11">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>108.6160499487212</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
@@ -711,16 +711,16 @@
         <v>180.2347174069558</v>
       </c>
       <c r="U2" t="n">
-        <v>232</v>
+        <v>60.01805955641076</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>101.313901802988</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>192.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -760,49 +760,49 @@
         <v>32.41397866798465</v>
       </c>
       <c r="K3" t="n">
-        <v>209.6535371656184</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>175.0656026205451</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="N3" t="n">
         <v>232</v>
       </c>
       <c r="O3" t="n">
-        <v>42.20368154585192</v>
+        <v>7.767434760836147</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>187.1553865711792</v>
       </c>
       <c r="Q3" t="n">
-        <v>72.58809527915881</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>98.39553314143586</v>
+        <v>232</v>
       </c>
       <c r="S3" t="n">
-        <v>51.9412641155547</v>
+        <v>232</v>
       </c>
       <c r="T3" t="n">
         <v>2.184614274117564</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1585673073565772</v>
+        <v>149.9251033706662</v>
       </c>
       <c r="V3" t="n">
         <v>232</v>
       </c>
       <c r="W3" t="n">
-        <v>191.214786436989</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -851,13 +851,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>11.16632944592679</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.16632944592679</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.99931295557451</v>
+        <v>81.25951104779007</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.286015503096621</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -918,7 +918,7 @@
         <v>142.1634384058943</v>
       </c>
       <c r="K5" t="n">
-        <v>44.8378994974874</v>
+        <v>44.83789949748741</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -945,19 +945,19 @@
         <v>61.31962508875506</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>180.2347174069558</v>
       </c>
       <c r="U5" t="n">
-        <v>199.5493062543692</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
         <v>232</v>
       </c>
       <c r="X5" t="n">
-        <v>192.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>144.3309763356402</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -997,25 +997,25 @@
         <v>227.3832</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>209.6535371656184</v>
       </c>
       <c r="L6" t="n">
-        <v>175.0656026205451</v>
+        <v>22.30006283438168</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O6" t="n">
-        <v>185.9190976528743</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>102.9688997265807</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>72.58809527915881</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>98.39553314143586</v>
@@ -1024,10 +1024,10 @@
         <v>51.9412641155547</v>
       </c>
       <c r="T6" t="n">
-        <v>2.184614274117564</v>
+        <v>232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1585673073565772</v>
+        <v>232</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>219.2622531962733</v>
       </c>
     </row>
     <row r="7">
@@ -1088,13 +1088,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>11.16632944592679</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1131,19 +1131,19 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>2.286015503096621</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1161,13 +1161,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>217.994657849159</v>
+        <v>232</v>
       </c>
       <c r="N8" t="n">
         <v>232</v>
       </c>
       <c r="O8" t="n">
-        <v>54.34080424745926</v>
+        <v>40.33546209661831</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>101.4212954206196</v>
+        <v>61.31962508875506</v>
       </c>
       <c r="T8" t="n">
         <v>180.2347174069558</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>25.9638939573787</v>
       </c>
       <c r="W8" t="n">
-        <v>161.7383402725551</v>
+        <v>232</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>219.1036858889167</v>
+        <v>83.31460475623481</v>
       </c>
       <c r="E9" t="n">
         <v>232</v>
@@ -1234,19 +1234,19 @@
         <v>227.3832</v>
       </c>
       <c r="K9" t="n">
-        <v>209.6535371656184</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>175.0656026205451</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>102.9688997265807</v>
       </c>
       <c r="N9" t="n">
-        <v>79.23446021383661</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>185.9190976528743</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1255,13 +1255,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>98.39553314143586</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>51.9412641155547</v>
       </c>
       <c r="T9" t="n">
-        <v>232</v>
+        <v>2.184614274117564</v>
       </c>
       <c r="U9" t="n">
         <v>0.1585673073565772</v>
@@ -1325,25 +1325,25 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>11.16632944592679</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="C11" t="n">
-        <v>222.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>183.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>177.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>177.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>90.61810344212547</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,25 +1416,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>75.64315465328136</v>
+      </c>
+      <c r="Y11" t="n">
         <v>232</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1444,22 +1444,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>157.5565566463266</v>
+        <v>19.80533886820345</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>134.0999124455193</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>115.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>97.95229059200848</v>
       </c>
       <c r="H12" t="n">
         <v>97.56495511094943</v>
@@ -1498,22 +1498,22 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>149.1785843839036</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>173.1585673073565</v>
       </c>
       <c r="V12" t="n">
-        <v>187.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>205.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>192.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>172.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>14.7555239627632</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1556,22 +1556,22 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>190.1736114025499</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>232</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>204.9291353653131</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>89.0653182199393</v>
       </c>
       <c r="D14" t="n">
         <v>182.3391557398498</v>
@@ -1614,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>176.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>174.2860155030966</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>164.9411260402108</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>201.8896740088309</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1681,22 +1681,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96.77602671251378</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>133.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>119.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>114.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>111.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>96.95229059200848</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>219.1829098905474</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>172.1585673073565</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>186.5106671915202</v>
@@ -1747,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>191.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>171.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>16.38387284153003</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1790,19 +1790,19 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>97.42362815777916</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>189.1736114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>175.9623170936755</v>
+        <v>97.72724295552162</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1826,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>19.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>59.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>182.3391557398498</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>174.2860155030966</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1890,25 +1890,25 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
         <v>232</v>
       </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>79.7204287570534</v>
       </c>
       <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
         <v>232</v>
       </c>
-      <c r="W17" t="n">
-        <v>204.3455999999999</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
       <c r="Y17" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>133.0999124455193</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>111.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.237619015483655</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>117.4035241897422</v>
       </c>
       <c r="T18" t="n">
         <v>174.1846142741176</v>
       </c>
       <c r="U18" t="n">
-        <v>172.1585673073565</v>
+        <v>172.1585673073566</v>
       </c>
       <c r="V18" t="n">
-        <v>186.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>191.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>171.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1997,22 +1997,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>59.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>23.84590450028551</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>52.98090483695654</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>16.38387284153004</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2033,11 +2033,11 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>232</v>
       </c>
-      <c r="O19" t="n">
-        <v>88.91835566245766</v>
-      </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>122.8714797028554</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>59.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2091,10 +2091,10 @@
         <v>176.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>174.2860155030966</v>
       </c>
       <c r="H20" t="n">
-        <v>164.9411260402108</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,22 +2127,22 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>232</v>
       </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>232</v>
+        <v>85.16995578889153</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>94.5148452517772</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>156.5565566463266</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>111.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>96.95229059200848</v>
       </c>
       <c r="H21" t="n">
         <v>96.56495511094943</v>
@@ -2212,19 +2212,19 @@
         <v>174.1846142741176</v>
       </c>
       <c r="U21" t="n">
-        <v>172.1585673073565</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>186.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>159.2905537781793</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>18.18512341894315</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>171.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2234,22 +2234,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>59.11380033707866</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>44.72524664804467</v>
       </c>
       <c r="D22" t="n">
-        <v>35.45720892796405</v>
+        <v>57.53621805555548</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>46.38285596774193</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>16.38387284153003</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2264,13 +2264,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>97.42362815777916</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>200.2041960852548</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>19.44364543010755</v>
       </c>
       <c r="Y22" t="n">
-        <v>59.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2316,10 +2316,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>221.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>182.3391557398498</v>
       </c>
       <c r="E23" t="n">
         <v>176.3632896068686</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>95.04118435292044</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>164.9411260402108</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>155.2274503700768</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>6.243835818576555</v>
       </c>
       <c r="C24" t="n">
         <v>133.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>119.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>114.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>111.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>96.56495511094943</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,16 +2440,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.81790954590688</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>174.1846142741176</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>172.1585673073565</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>186.5106671915202</v>
@@ -2458,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>191.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>171.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>48.4054084925534</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>57.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>52.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>46.38285596774193</v>
@@ -2513,14 +2513,14 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
         <v>232</v>
       </c>
-      <c r="Q25" t="n">
-        <v>54.88985650505919</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>59.46535284946236</v>
       </c>
     </row>
     <row r="26">
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>177.0000000000014</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>177.0000000000014</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>177.0000000000029</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2583,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>73.90475075789521</v>
+        <v>92.34692529528144</v>
       </c>
       <c r="N26" t="n">
-        <v>21.1532632604878</v>
+        <v>2.711088723101568</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2601,10 +2601,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>177.0000000000024</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>155.9015999999949</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2613,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>177.0000000000013</v>
+        <v>155.9015999999941</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>177.0000000000014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2632,22 +2632,22 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>67.13832783954992</v>
+        <v>149.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>135.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>130.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>127.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>112.9522905920085</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>112.5649551109494</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>53.12959033256555</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2695,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>177.0000000000013</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>177.0000000000013</v>
       </c>
     </row>
     <row r="28">
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>60.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -2720,13 +2720,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>62.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>32.38387284153004</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>10.90312610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2747,13 +2747,13 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>48.65281593332151</v>
+        <v>127.8860801804288</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>14.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>75.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>155.9016</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>177</v>
       </c>
       <c r="H29" t="n">
-        <v>155.9016</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,22 +2838,22 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
         <v>177</v>
       </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>135.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>130.6720972219126</v>
@@ -2881,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>112.9522905920085</v>
+        <v>66.29181588038472</v>
       </c>
       <c r="H30" t="n">
-        <v>112.5649551109494</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2923,19 +2923,19 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>153.7122570751294</v>
+        <v>177</v>
       </c>
       <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
         <v>177</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2945,25 +2945,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>75.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>60.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>73.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>62.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4.777977564642218</v>
       </c>
       <c r="H31" t="n">
-        <v>10.90312610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>113.4236281577792</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>31.9093075283969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>56.25229489003472</v>
+      </c>
+      <c r="C32" t="n">
         <v>177</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>137.2860155030966</v>
       </c>
       <c r="H32" t="n">
-        <v>56.25229489003472</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3075,16 +3075,16 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>177</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>96.09991244551929</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3118,10 +3118,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>59.95229059200847</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>59.56495511094943</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,19 +3151,19 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>163.595766527619</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>137.1846142741176</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>135.1585673073566</v>
+        <v>128.6195548939999</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>149.5106671915202</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -3172,7 +3172,7 @@
         <v>154.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>134.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -3212,22 +3212,22 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>60.42362815777915</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>152.1736114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>177</v>
       </c>
       <c r="P34" t="n">
-        <v>168.5150778546622</v>
+        <v>177</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>76.76509460989148</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3267,19 +3267,19 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>145.3391557398498</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>139.8896287080119</v>
       </c>
       <c r="G35" t="n">
         <v>137.2860155030966</v>
       </c>
       <c r="H35" t="n">
-        <v>127.9411260402108</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3294,11 +3294,11 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>95.05801401838302</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -3312,19 +3312,19 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>67.67445845669249</v>
+        <v>177</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>87.38680004904175</v>
       </c>
       <c r="W35" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3343,10 +3343,10 @@
         <v>119.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>96.09991244551929</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>82.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3358,7 +3358,7 @@
         <v>59.95229059200847</v>
       </c>
       <c r="H36" t="n">
-        <v>59.56495511094943</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3394,22 +3394,22 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>137.1846142741176</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>6.317763938148429</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>39.29121652422917</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>154.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>134.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3431,7 +3431,7 @@
         <v>15.98090483695654</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>9.382855967741932</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3449,16 +3449,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>60.42362815777915</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>51.93870601244139</v>
       </c>
       <c r="P37" t="n">
         <v>177</v>
@@ -3467,10 +3467,10 @@
         <v>177</v>
       </c>
       <c r="R37" t="n">
-        <v>92.0264541195487</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>85.87147970285542</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>139.3632896068686</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>16.53831039313133</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3531,10 +3531,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>20.90475075789521</v>
       </c>
       <c r="N38" t="n">
-        <v>95.05801401838302</v>
+        <v>74.15326326048778</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -3561,10 +3561,10 @@
         <v>177</v>
       </c>
       <c r="W38" t="n">
-        <v>155.9016</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>119.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>96.09991244551929</v>
@@ -3592,10 +3592,10 @@
         <v>74.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>59.95229059200847</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>59.56495511094943</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,28 +3625,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>56.96934169549915</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>137.1846142741176</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>135.1585673073566</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>149.5106671915202</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>14.16713105389009</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>134.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>60.42362815777915</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3695,16 +3695,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>177</v>
+        <v>143.0672263095859</v>
       </c>
       <c r="P40" t="n">
         <v>177</v>
       </c>
       <c r="Q40" t="n">
-        <v>82.64359815180674</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="S40" t="n">
         <v>85.87147970285542</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3744,16 +3744,16 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>116.5449227293757</v>
       </c>
       <c r="I41" t="n">
         <v>39.35667727062432</v>
@@ -3768,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>95.05801401838302</v>
       </c>
       <c r="N41" t="n">
-        <v>95.05801401838302</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>104.453483250405</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>177</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>12.09143947897063</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3832,10 +3832,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="I42" t="n">
-        <v>136.0216689102165</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,25 +3859,25 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18.58809527915881</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>155.9016</v>
+      </c>
+      <c r="V42" t="n">
         <v>177</v>
       </c>
-      <c r="S42" t="n">
-        <v>177</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.291835810624601</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
       <c r="W42" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>64.09172944592679</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>64.09172944592679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>40.35667727062432</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,16 +4020,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>105.453483250405</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
+        <v>50.44811674959501</v>
+      </c>
+      <c r="U44" t="n">
         <v>177</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4038,10 +4038,10 @@
         <v>177</v>
       </c>
       <c r="X44" t="n">
-        <v>115.5449227293757</v>
+        <v>177</v>
       </c>
       <c r="Y44" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4057,10 +4057,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>136.3135047208412</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>137.0216689102165</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>176.2918358106247</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4130,64 +4130,64 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
         <v>63.11162944592679</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.65908036144133</v>
+        <v>195.9392203461348</v>
       </c>
       <c r="C2" t="n">
-        <v>40.65908036144133</v>
+        <v>145.9648988885652</v>
       </c>
       <c r="D2" t="n">
-        <v>30.2154887050274</v>
+        <v>135.5213072321512</v>
       </c>
       <c r="E2" t="n">
         <v>25.80812546576614</v>
@@ -4354,19 +4354,19 @@
         <v>684.005714650797</v>
       </c>
       <c r="U2" t="n">
-        <v>449.6622803073627</v>
+        <v>623.3814120685639</v>
       </c>
       <c r="V2" t="n">
-        <v>449.6622803073627</v>
+        <v>391.2086603849034</v>
       </c>
       <c r="W2" t="n">
-        <v>347.3250057588899</v>
+        <v>391.2086603849034</v>
       </c>
       <c r="X2" t="n">
-        <v>153.1009315561953</v>
+        <v>391.2086603849034</v>
       </c>
       <c r="Y2" t="n">
-        <v>40.65908036144133</v>
+        <v>278.7668091901494</v>
       </c>
     </row>
     <row r="3">
@@ -4403,46 +4403,46 @@
         <v>215.4986074060761</v>
       </c>
       <c r="K3" t="n">
-        <v>233.4073577438353</v>
+        <v>445.1786074060761</v>
       </c>
       <c r="L3" t="n">
-        <v>286.2534157028807</v>
+        <v>674.8586074060761</v>
       </c>
       <c r="M3" t="n">
-        <v>515.9334157028807</v>
+        <v>670.1951730626417</v>
       </c>
       <c r="N3" t="n">
-        <v>511.2699813594463</v>
+        <v>665.5317387192074</v>
       </c>
       <c r="O3" t="n">
-        <v>698.3199999999999</v>
+        <v>887.3658450213932</v>
       </c>
       <c r="P3" t="n">
         <v>928</v>
       </c>
       <c r="Q3" t="n">
-        <v>854.6786916372133</v>
+        <v>928</v>
       </c>
       <c r="R3" t="n">
-        <v>755.2892642216216</v>
+        <v>693.6565656565656</v>
       </c>
       <c r="S3" t="n">
-        <v>702.8233408725764</v>
+        <v>459.3131313131312</v>
       </c>
       <c r="T3" t="n">
-        <v>700.6166597876091</v>
+        <v>457.106450228164</v>
       </c>
       <c r="U3" t="n">
-        <v>700.4564907902793</v>
+        <v>305.6669518739557</v>
       </c>
       <c r="V3" t="n">
-        <v>466.113056446845</v>
+        <v>71.32351753052129</v>
       </c>
       <c r="W3" t="n">
-        <v>272.9668075205935</v>
+        <v>38.62337317715914</v>
       </c>
       <c r="X3" t="n">
-        <v>252.9034343434344</v>
+        <v>18.56</v>
       </c>
       <c r="Y3" t="n">
         <v>18.56</v>
@@ -4494,10 +4494,10 @@
         <v>29.83912065245131</v>
       </c>
       <c r="O4" t="n">
-        <v>29.83912065245131</v>
+        <v>18.56</v>
       </c>
       <c r="P4" t="n">
-        <v>29.83912065245131</v>
+        <v>18.56</v>
       </c>
       <c r="Q4" t="n">
         <v>18.56</v>
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.65908036144133</v>
+        <v>22.96736323926126</v>
       </c>
       <c r="C5" t="n">
-        <v>40.65908036144133</v>
+        <v>22.96736323926126</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2154887050274</v>
+        <v>22.96736323926126</v>
       </c>
       <c r="E5" t="n">
-        <v>25.80812546576614</v>
+        <v>18.56</v>
       </c>
       <c r="F5" t="n">
-        <v>20.86910656878446</v>
+        <v>18.56</v>
       </c>
       <c r="G5" t="n">
         <v>18.56</v>
@@ -4588,22 +4588,22 @@
         <v>866.0609847588332</v>
       </c>
       <c r="T5" t="n">
-        <v>866.0609847588332</v>
+        <v>684.005714650797</v>
       </c>
       <c r="U5" t="n">
-        <v>664.496028946339</v>
+        <v>684.005714650797</v>
       </c>
       <c r="V5" t="n">
-        <v>664.496028946339</v>
+        <v>451.8329629671365</v>
       </c>
       <c r="W5" t="n">
-        <v>430.1525946029046</v>
+        <v>217.4895286237021</v>
       </c>
       <c r="X5" t="n">
-        <v>235.9285204002099</v>
+        <v>217.4895286237021</v>
       </c>
       <c r="Y5" t="n">
-        <v>123.486669205456</v>
+        <v>105.0476774289482</v>
       </c>
     </row>
     <row r="6">
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>633.0357336723639</v>
+        <v>18.56</v>
       </c>
       <c r="C6" t="n">
-        <v>633.0357336723639</v>
+        <v>18.56</v>
       </c>
       <c r="D6" t="n">
-        <v>398.6922993289296</v>
+        <v>18.56</v>
       </c>
       <c r="E6" t="n">
-        <v>252.9034343434344</v>
+        <v>18.56</v>
       </c>
       <c r="F6" t="n">
-        <v>252.9034343434344</v>
+        <v>18.56</v>
       </c>
       <c r="G6" t="n">
         <v>18.56</v>
@@ -4640,49 +4640,49 @@
         <v>18.56</v>
       </c>
       <c r="K6" t="n">
-        <v>248.24</v>
+        <v>36.46875033775919</v>
       </c>
       <c r="L6" t="n">
-        <v>301.0860579590454</v>
+        <v>243.6234343434343</v>
       </c>
       <c r="M6" t="n">
-        <v>530.7660579590454</v>
+        <v>473.3034343434343</v>
       </c>
       <c r="N6" t="n">
-        <v>760.4460579590454</v>
+        <v>468.6399999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>802.3289896228088</v>
+        <v>698.3199999999999</v>
       </c>
       <c r="P6" t="n">
         <v>928</v>
       </c>
       <c r="Q6" t="n">
-        <v>854.6786916372133</v>
+        <v>928</v>
       </c>
       <c r="R6" t="n">
-        <v>755.2892642216216</v>
+        <v>828.6105725844083</v>
       </c>
       <c r="S6" t="n">
-        <v>702.8233408725764</v>
+        <v>776.1446492353631</v>
       </c>
       <c r="T6" t="n">
-        <v>700.6166597876091</v>
+        <v>541.8012148919288</v>
       </c>
       <c r="U6" t="n">
-        <v>700.4564907902793</v>
+        <v>307.4577805484944</v>
       </c>
       <c r="V6" t="n">
-        <v>685.7992512028852</v>
+        <v>292.8005409611004</v>
       </c>
       <c r="W6" t="n">
-        <v>653.0991068495231</v>
+        <v>260.1003966077382</v>
       </c>
       <c r="X6" t="n">
-        <v>633.0357336723639</v>
+        <v>240.0370234305791</v>
       </c>
       <c r="Y6" t="n">
-        <v>633.0357336723639</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="7">
@@ -4731,10 +4731,10 @@
         <v>29.83912065245131</v>
       </c>
       <c r="O7" t="n">
-        <v>18.56</v>
+        <v>29.83912065245131</v>
       </c>
       <c r="P7" t="n">
-        <v>18.56</v>
+        <v>29.83912065245131</v>
       </c>
       <c r="Q7" t="n">
         <v>18.56</v>
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>90.63340181901094</v>
+        <v>33.9426105533956</v>
       </c>
       <c r="C8" t="n">
-        <v>40.65908036144133</v>
+        <v>33.9426105533956</v>
       </c>
       <c r="D8" t="n">
-        <v>30.2154887050274</v>
+        <v>23.49901889698167</v>
       </c>
       <c r="E8" t="n">
-        <v>25.80812546576614</v>
+        <v>23.49901889698167</v>
       </c>
       <c r="F8" t="n">
-        <v>20.86910656878446</v>
+        <v>18.56</v>
       </c>
       <c r="G8" t="n">
         <v>18.56</v>
@@ -4804,10 +4804,10 @@
         <v>518.7097596935538</v>
       </c>
       <c r="M8" t="n">
-        <v>528.1931356034942</v>
+        <v>514.0463253501194</v>
       </c>
       <c r="N8" t="n">
-        <v>523.5297012600598</v>
+        <v>509.3828910066851</v>
       </c>
       <c r="O8" t="n">
         <v>698.3199999999999</v>
@@ -4822,25 +4822,25 @@
         <v>928</v>
       </c>
       <c r="S8" t="n">
-        <v>825.5542470498792</v>
+        <v>866.0609847588332</v>
       </c>
       <c r="T8" t="n">
-        <v>643.498976941843</v>
+        <v>684.005714650797</v>
       </c>
       <c r="U8" t="n">
-        <v>643.498976941843</v>
+        <v>684.005714650797</v>
       </c>
       <c r="V8" t="n">
-        <v>643.498976941843</v>
+        <v>657.7795591382933</v>
       </c>
       <c r="W8" t="n">
-        <v>480.1269160604742</v>
+        <v>423.4361247948589</v>
       </c>
       <c r="X8" t="n">
-        <v>285.9028418577795</v>
+        <v>229.2120505921642</v>
       </c>
       <c r="Y8" t="n">
-        <v>173.4609906630256</v>
+        <v>116.7701993974103</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>474.2202887766836</v>
+        <v>571.4030351073079</v>
       </c>
       <c r="C9" t="n">
-        <v>474.2202887766836</v>
+        <v>337.0596007638736</v>
       </c>
       <c r="D9" t="n">
         <v>252.9034343434344</v>
@@ -4877,16 +4877,16 @@
         <v>18.56</v>
       </c>
       <c r="K9" t="n">
-        <v>36.46875033775919</v>
+        <v>248.24</v>
       </c>
       <c r="L9" t="n">
-        <v>89.31480829680459</v>
+        <v>301.0860579590454</v>
       </c>
       <c r="M9" t="n">
-        <v>318.9948082968046</v>
+        <v>426.7570683362366</v>
       </c>
       <c r="N9" t="n">
-        <v>468.6399999999999</v>
+        <v>656.4370683362366</v>
       </c>
       <c r="O9" t="n">
         <v>698.3199999999999</v>
@@ -4898,28 +4898,28 @@
         <v>928</v>
       </c>
       <c r="R9" t="n">
-        <v>828.6105725844083</v>
+        <v>928</v>
       </c>
       <c r="S9" t="n">
-        <v>776.1446492353631</v>
+        <v>875.5340766509548</v>
       </c>
       <c r="T9" t="n">
-        <v>541.8012148919288</v>
+        <v>873.3273955659876</v>
       </c>
       <c r="U9" t="n">
-        <v>541.641045894599</v>
+        <v>873.1672265686577</v>
       </c>
       <c r="V9" t="n">
-        <v>526.9838063072049</v>
+        <v>858.5099869812636</v>
       </c>
       <c r="W9" t="n">
-        <v>494.2836619538427</v>
+        <v>825.8098426279015</v>
       </c>
       <c r="X9" t="n">
-        <v>474.2202887766836</v>
+        <v>805.7464694507423</v>
       </c>
       <c r="Y9" t="n">
-        <v>474.2202887766836</v>
+        <v>805.7464694507423</v>
       </c>
     </row>
     <row r="10">
@@ -4968,22 +4968,22 @@
         <v>29.83912065245131</v>
       </c>
       <c r="O10" t="n">
-        <v>18.56</v>
+        <v>29.83912065245131</v>
       </c>
       <c r="P10" t="n">
-        <v>18.56</v>
+        <v>29.83912065245131</v>
       </c>
       <c r="Q10" t="n">
-        <v>18.56</v>
+        <v>29.83912065245131</v>
       </c>
       <c r="R10" t="n">
-        <v>18.56</v>
+        <v>29.83912065245131</v>
       </c>
       <c r="S10" t="n">
-        <v>18.56</v>
+        <v>29.83912065245131</v>
       </c>
       <c r="T10" t="n">
-        <v>18.56</v>
+        <v>29.83912065245131</v>
       </c>
       <c r="U10" t="n">
         <v>18.56</v>
@@ -5008,40 +5008,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>693.6565656565656</v>
+        <v>382.9059043906248</v>
       </c>
       <c r="C11" t="n">
-        <v>468.9347694515212</v>
+        <v>382.9059043906248</v>
       </c>
       <c r="D11" t="n">
-        <v>468.9347694515212</v>
+        <v>197.714837986736</v>
       </c>
       <c r="E11" t="n">
-        <v>289.7799314647852</v>
+        <v>18.56</v>
       </c>
       <c r="F11" t="n">
-        <v>110.0934378203288</v>
+        <v>18.56</v>
       </c>
       <c r="G11" t="n">
-        <v>110.0934378203288</v>
+        <v>18.56</v>
       </c>
       <c r="H11" t="n">
         <v>18.56</v>
       </c>
       <c r="I11" t="n">
-        <v>31.4263439355395</v>
+        <v>39.02579489322527</v>
       </c>
       <c r="J11" t="n">
-        <v>120.3645399137041</v>
+        <v>127.9639908713899</v>
       </c>
       <c r="K11" t="n">
-        <v>305.6550194111916</v>
+        <v>313.2544703688773</v>
       </c>
       <c r="L11" t="n">
-        <v>535.3350194111915</v>
+        <v>542.9344703688773</v>
       </c>
       <c r="M11" t="n">
-        <v>535.3350194111915</v>
+        <v>542.9344703688773</v>
       </c>
       <c r="N11" t="n">
         <v>542.9344703688773</v>
@@ -5059,25 +5059,25 @@
         <v>928</v>
       </c>
       <c r="S11" t="n">
-        <v>693.6565656565656</v>
+        <v>928</v>
       </c>
       <c r="T11" t="n">
-        <v>693.6565656565656</v>
+        <v>928</v>
       </c>
       <c r="U11" t="n">
-        <v>693.6565656565656</v>
+        <v>928</v>
       </c>
       <c r="V11" t="n">
-        <v>693.6565656565656</v>
+        <v>928</v>
       </c>
       <c r="W11" t="n">
-        <v>693.6565656565656</v>
+        <v>928</v>
       </c>
       <c r="X11" t="n">
-        <v>693.6565656565656</v>
+        <v>851.5927730774936</v>
       </c>
       <c r="Y11" t="n">
-        <v>693.6565656565656</v>
+        <v>617.2493387340592</v>
       </c>
     </row>
     <row r="12">
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>233.9509619523859</v>
+        <v>351.5066243924012</v>
       </c>
       <c r="C12" t="n">
-        <v>233.9509619523859</v>
+        <v>216.0521673767252</v>
       </c>
       <c r="D12" t="n">
-        <v>233.9509619523859</v>
+        <v>216.0521673767252</v>
       </c>
       <c r="E12" t="n">
-        <v>117.1104597080297</v>
+        <v>216.0521673767252</v>
       </c>
       <c r="F12" t="n">
-        <v>117.1104597080297</v>
+        <v>216.0521673767252</v>
       </c>
       <c r="G12" t="n">
         <v>117.1104597080297</v>
@@ -5108,25 +5108,25 @@
         <v>18.56</v>
       </c>
       <c r="I12" t="n">
-        <v>37.61824170528192</v>
+        <v>18.56</v>
       </c>
       <c r="J12" t="n">
-        <v>37.61824170528192</v>
+        <v>216.1501611186952</v>
       </c>
       <c r="K12" t="n">
-        <v>59.7412399113197</v>
+        <v>445.8301611186952</v>
       </c>
       <c r="L12" t="n">
-        <v>289.4212399113197</v>
+        <v>502.1952145243555</v>
       </c>
       <c r="M12" t="n">
-        <v>313.9728408220104</v>
+        <v>502.1952145243555</v>
       </c>
       <c r="N12" t="n">
-        <v>394.1305671148476</v>
+        <v>684.3108236862421</v>
       </c>
       <c r="O12" t="n">
-        <v>623.8105671148476</v>
+        <v>747.8384904219328</v>
       </c>
       <c r="P12" t="n">
         <v>792.2346577164653</v>
@@ -5141,22 +5141,22 @@
         <v>928</v>
       </c>
       <c r="T12" t="n">
-        <v>777.3145612283802</v>
+        <v>928</v>
       </c>
       <c r="U12" t="n">
-        <v>777.3145612283802</v>
+        <v>753.0923562551955</v>
       </c>
       <c r="V12" t="n">
-        <v>587.9098468935114</v>
+        <v>753.0923562551955</v>
       </c>
       <c r="W12" t="n">
-        <v>587.9098468935114</v>
+        <v>545.6447371543586</v>
       </c>
       <c r="X12" t="n">
-        <v>393.0989989688775</v>
+        <v>545.6447371543586</v>
       </c>
       <c r="Y12" t="n">
-        <v>393.0989989688775</v>
+        <v>371.5120171885663</v>
       </c>
     </row>
     <row r="13">
@@ -5178,40 +5178,40 @@
         <v>141.6466229427149</v>
       </c>
       <c r="F13" t="n">
-        <v>126.7420532833581</v>
+        <v>141.6466229427149</v>
       </c>
       <c r="G13" t="n">
-        <v>126.7420532833581</v>
+        <v>141.6466229427149</v>
       </c>
       <c r="H13" t="n">
-        <v>130.7979584427557</v>
+        <v>145.7025281021125</v>
       </c>
       <c r="I13" t="n">
-        <v>200.3103573788386</v>
+        <v>215.2149270381954</v>
       </c>
       <c r="J13" t="n">
-        <v>429.9903573788386</v>
+        <v>444.8949270381954</v>
       </c>
       <c r="K13" t="n">
-        <v>444.997991315707</v>
+        <v>459.9025609750638</v>
       </c>
       <c r="L13" t="n">
-        <v>444.997991315707</v>
+        <v>459.9025609750638</v>
       </c>
       <c r="M13" t="n">
-        <v>252.9034343434344</v>
+        <v>459.9025609750638</v>
       </c>
       <c r="N13" t="n">
-        <v>18.56</v>
+        <v>459.9025609750638</v>
       </c>
       <c r="O13" t="n">
-        <v>18.56</v>
+        <v>459.9025609750638</v>
       </c>
       <c r="P13" t="n">
-        <v>18.56</v>
+        <v>225.5591266316295</v>
       </c>
       <c r="Q13" t="n">
-        <v>18.56</v>
+        <v>225.5591266316295</v>
       </c>
       <c r="R13" t="n">
         <v>18.56</v>
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>724.0710363547163</v>
+        <v>459.3131313131312</v>
       </c>
       <c r="C14" t="n">
-        <v>724.0710363547163</v>
+        <v>369.3481634142026</v>
       </c>
       <c r="D14" t="n">
-        <v>539.8900709609286</v>
+        <v>185.167198020415</v>
       </c>
       <c r="E14" t="n">
-        <v>539.8900709609286</v>
+        <v>185.167198020415</v>
       </c>
       <c r="F14" t="n">
-        <v>361.2136783265732</v>
+        <v>185.167198020415</v>
       </c>
       <c r="G14" t="n">
         <v>185.167198020415</v>
@@ -5266,7 +5266,7 @@
         <v>18.56</v>
       </c>
       <c r="I14" t="n">
-        <v>39.02579489322527</v>
+        <v>18.56</v>
       </c>
       <c r="J14" t="n">
         <v>127.9639908713899</v>
@@ -5296,25 +5296,25 @@
         <v>928</v>
       </c>
       <c r="S14" t="n">
-        <v>928</v>
+        <v>693.6565656565656</v>
       </c>
       <c r="T14" t="n">
-        <v>928</v>
+        <v>693.6565656565656</v>
       </c>
       <c r="U14" t="n">
-        <v>724.0710363547163</v>
+        <v>693.6565656565656</v>
       </c>
       <c r="V14" t="n">
-        <v>724.0710363547163</v>
+        <v>693.6565656565656</v>
       </c>
       <c r="W14" t="n">
-        <v>724.0710363547163</v>
+        <v>693.6565656565656</v>
       </c>
       <c r="X14" t="n">
-        <v>724.0710363547163</v>
+        <v>459.3131313131312</v>
       </c>
       <c r="Y14" t="n">
-        <v>724.0710363547163</v>
+        <v>459.3131313131312</v>
       </c>
     </row>
     <row r="15">
@@ -5324,19 +5324,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>274.1535346901231</v>
+        <v>345.0858890422202</v>
       </c>
       <c r="C15" t="n">
-        <v>139.7091786845481</v>
+        <v>345.0858890422202</v>
       </c>
       <c r="D15" t="n">
-        <v>18.56</v>
+        <v>345.0858890422202</v>
       </c>
       <c r="E15" t="n">
-        <v>18.56</v>
+        <v>229.255487807965</v>
       </c>
       <c r="F15" t="n">
-        <v>18.56</v>
+        <v>116.4916066585944</v>
       </c>
       <c r="G15" t="n">
         <v>18.56</v>
@@ -5345,28 +5345,28 @@
         <v>18.56</v>
       </c>
       <c r="I15" t="n">
-        <v>56.1585477788857</v>
+        <v>18.56</v>
       </c>
       <c r="J15" t="n">
-        <v>254.2786143890704</v>
+        <v>18.56</v>
       </c>
       <c r="K15" t="n">
-        <v>276.4016125951081</v>
+        <v>248.24</v>
       </c>
       <c r="L15" t="n">
-        <v>332.7666660007685</v>
+        <v>477.92</v>
       </c>
       <c r="M15" t="n">
-        <v>450.4438304912367</v>
+        <v>707.6</v>
       </c>
       <c r="N15" t="n">
-        <v>531.5915567840739</v>
+        <v>707.6</v>
       </c>
       <c r="O15" t="n">
-        <v>729.7460470318347</v>
+        <v>753.2200933236545</v>
       </c>
       <c r="P15" t="n">
-        <v>774.1422143263673</v>
+        <v>797.6162606181871</v>
       </c>
       <c r="Q15" t="n">
         <v>928</v>
@@ -5375,25 +5375,25 @@
         <v>928</v>
       </c>
       <c r="S15" t="n">
-        <v>928</v>
+        <v>706.6031213226794</v>
       </c>
       <c r="T15" t="n">
-        <v>928</v>
+        <v>706.6031213226794</v>
       </c>
       <c r="U15" t="n">
-        <v>754.1024572652964</v>
+        <v>706.6031213226794</v>
       </c>
       <c r="V15" t="n">
-        <v>565.7078439405285</v>
+        <v>518.2085079979115</v>
       </c>
       <c r="W15" t="n">
-        <v>565.7078439405285</v>
+        <v>518.2085079979115</v>
       </c>
       <c r="X15" t="n">
-        <v>371.9070970259957</v>
+        <v>518.2085079979115</v>
       </c>
       <c r="Y15" t="n">
-        <v>371.9070970259957</v>
+        <v>345.0858890422202</v>
       </c>
     </row>
     <row r="16">
@@ -5403,46 +5403,46 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>125.9665770537173</v>
+        <v>85.54060996345996</v>
       </c>
       <c r="C16" t="n">
-        <v>125.9665770537173</v>
+        <v>85.54060996345996</v>
       </c>
       <c r="D16" t="n">
-        <v>125.9665770537173</v>
+        <v>85.54060996345996</v>
       </c>
       <c r="E16" t="n">
-        <v>125.9665770537173</v>
+        <v>85.54060996345996</v>
       </c>
       <c r="F16" t="n">
-        <v>125.9665770537173</v>
+        <v>85.54060996345996</v>
       </c>
       <c r="G16" t="n">
-        <v>109.4172105471214</v>
+        <v>85.54060996345996</v>
       </c>
       <c r="H16" t="n">
-        <v>114.4631157065189</v>
+        <v>90.58651512285752</v>
       </c>
       <c r="I16" t="n">
-        <v>184.9655146426018</v>
+        <v>161.0889140589404</v>
       </c>
       <c r="J16" t="n">
-        <v>414.6455146426018</v>
+        <v>390.7689140589404</v>
       </c>
       <c r="K16" t="n">
-        <v>430.6431485794702</v>
+        <v>406.7665479958088</v>
       </c>
       <c r="L16" t="n">
-        <v>430.6431485794702</v>
+        <v>308.3588427859308</v>
       </c>
       <c r="M16" t="n">
-        <v>430.6431485794702</v>
+        <v>117.2743868237592</v>
       </c>
       <c r="N16" t="n">
-        <v>252.9034343434344</v>
+        <v>18.56</v>
       </c>
       <c r="O16" t="n">
-        <v>252.9034343434344</v>
+        <v>18.56</v>
       </c>
       <c r="P16" t="n">
         <v>18.56</v>
@@ -5469,10 +5469,10 @@
         <v>145.6066229427149</v>
       </c>
       <c r="X16" t="n">
-        <v>125.9665770537173</v>
+        <v>145.6066229427149</v>
       </c>
       <c r="Y16" t="n">
-        <v>125.9665770537173</v>
+        <v>85.54060996345996</v>
       </c>
     </row>
     <row r="17">
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.56</v>
+        <v>378.7874456999459</v>
       </c>
       <c r="C17" t="n">
-        <v>18.56</v>
+        <v>378.7874456999459</v>
       </c>
       <c r="D17" t="n">
-        <v>18.56</v>
+        <v>194.6064803061582</v>
       </c>
       <c r="E17" t="n">
-        <v>18.56</v>
+        <v>194.6064803061582</v>
       </c>
       <c r="F17" t="n">
-        <v>18.56</v>
+        <v>194.6064803061582</v>
       </c>
       <c r="G17" t="n">
         <v>18.56</v>
@@ -5518,40 +5518,40 @@
         <v>522.4686754756519</v>
       </c>
       <c r="N17" t="n">
-        <v>522.4686754756519</v>
+        <v>542.9344703688773</v>
       </c>
       <c r="O17" t="n">
-        <v>698.3512792706672</v>
+        <v>718.8170741638927</v>
       </c>
       <c r="P17" t="n">
-        <v>907.5342051067745</v>
+        <v>928</v>
       </c>
       <c r="Q17" t="n">
-        <v>907.5342051067745</v>
+        <v>928</v>
       </c>
       <c r="R17" t="n">
         <v>928</v>
       </c>
       <c r="S17" t="n">
-        <v>693.6565656565656</v>
+        <v>928</v>
       </c>
       <c r="T17" t="n">
         <v>693.6565656565656</v>
       </c>
       <c r="U17" t="n">
-        <v>693.6565656565656</v>
+        <v>613.1308800433803</v>
       </c>
       <c r="V17" t="n">
-        <v>459.3131313131312</v>
+        <v>613.1308800433803</v>
       </c>
       <c r="W17" t="n">
-        <v>252.9034343434344</v>
+        <v>613.1308800433803</v>
       </c>
       <c r="X17" t="n">
-        <v>252.9034343434344</v>
+        <v>378.7874456999459</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.56</v>
+        <v>378.7874456999459</v>
       </c>
     </row>
     <row r="18">
@@ -5561,49 +5561,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22.84042324796329</v>
+        <v>265.7682371549456</v>
       </c>
       <c r="C18" t="n">
-        <v>22.84042324796329</v>
+        <v>131.3238811493706</v>
       </c>
       <c r="D18" t="n">
-        <v>22.84042324796329</v>
+        <v>131.3238811493706</v>
       </c>
       <c r="E18" t="n">
-        <v>22.84042324796329</v>
+        <v>131.3238811493706</v>
       </c>
       <c r="F18" t="n">
-        <v>22.84042324796329</v>
+        <v>18.56</v>
       </c>
       <c r="G18" t="n">
-        <v>22.84042324796329</v>
+        <v>18.56</v>
       </c>
       <c r="H18" t="n">
         <v>18.56</v>
       </c>
       <c r="I18" t="n">
-        <v>56.1585477788857</v>
+        <v>38.60824170528192</v>
       </c>
       <c r="J18" t="n">
-        <v>254.2786143890704</v>
+        <v>38.60824170528192</v>
       </c>
       <c r="K18" t="n">
-        <v>276.4016125951081</v>
+        <v>60.73123991131969</v>
       </c>
       <c r="L18" t="n">
-        <v>332.7666660007685</v>
+        <v>290.4112399113197</v>
       </c>
       <c r="M18" t="n">
-        <v>375.0646355178214</v>
+        <v>332.7092094283726</v>
       </c>
       <c r="N18" t="n">
-        <v>456.2123618106586</v>
+        <v>413.8569357212098</v>
       </c>
       <c r="O18" t="n">
-        <v>685.8923618106586</v>
+        <v>544.4622143263673</v>
       </c>
       <c r="P18" t="n">
-        <v>915.5723618106585</v>
+        <v>774.1422143263673</v>
       </c>
       <c r="Q18" t="n">
         <v>928</v>
@@ -5612,25 +5612,25 @@
         <v>928</v>
       </c>
       <c r="S18" t="n">
-        <v>928</v>
+        <v>809.410581626523</v>
       </c>
       <c r="T18" t="n">
-        <v>752.0559451776589</v>
+        <v>633.4665268041821</v>
       </c>
       <c r="U18" t="n">
-        <v>578.1584024429553</v>
+        <v>459.5689840694785</v>
       </c>
       <c r="V18" t="n">
-        <v>389.7637891181874</v>
+        <v>459.5689840694785</v>
       </c>
       <c r="W18" t="n">
-        <v>389.7637891181874</v>
+        <v>459.5689840694785</v>
       </c>
       <c r="X18" t="n">
-        <v>195.9630422036546</v>
+        <v>265.7682371549456</v>
       </c>
       <c r="Y18" t="n">
-        <v>22.84042324796329</v>
+        <v>265.7682371549456</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>145.6066229427149</v>
+        <v>112.7122042209819</v>
       </c>
       <c r="C19" t="n">
-        <v>145.6066229427149</v>
+        <v>88.62543199847129</v>
       </c>
       <c r="D19" t="n">
-        <v>145.6066229427149</v>
+        <v>88.62543199847129</v>
       </c>
       <c r="E19" t="n">
-        <v>145.6066229427149</v>
+        <v>35.10936650659599</v>
       </c>
       <c r="F19" t="n">
-        <v>145.6066229427149</v>
+        <v>35.10936650659599</v>
       </c>
       <c r="G19" t="n">
-        <v>145.6066229427149</v>
+        <v>18.56</v>
       </c>
       <c r="H19" t="n">
-        <v>150.6525281021124</v>
+        <v>23.60590515939756</v>
       </c>
       <c r="I19" t="n">
-        <v>221.1549270381954</v>
+        <v>94.10830409548049</v>
       </c>
       <c r="J19" t="n">
-        <v>450.8349270381954</v>
+        <v>323.7883040954805</v>
       </c>
       <c r="K19" t="n">
-        <v>466.8325609750638</v>
+        <v>339.7859380323489</v>
       </c>
       <c r="L19" t="n">
-        <v>466.8325609750638</v>
+        <v>339.7859380323489</v>
       </c>
       <c r="M19" t="n">
-        <v>466.8325609750638</v>
+        <v>339.7859380323489</v>
       </c>
       <c r="N19" t="n">
+        <v>339.7859380323489</v>
+      </c>
+      <c r="O19" t="n">
+        <v>105.4425036889145</v>
+      </c>
+      <c r="P19" t="n">
+        <v>105.4425036889145</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>105.4425036889145</v>
+      </c>
+      <c r="R19" t="n">
+        <v>105.4425036889145</v>
+      </c>
+      <c r="S19" t="n">
+        <v>105.4425036889145</v>
+      </c>
+      <c r="T19" t="n">
+        <v>126.0299828477194</v>
+      </c>
+      <c r="U19" t="n">
+        <v>202.336815486006</v>
+      </c>
+      <c r="V19" t="n">
+        <v>230.878208371952</v>
+      </c>
+      <c r="W19" t="n">
         <v>232.4891266316294</v>
       </c>
-      <c r="O19" t="n">
-        <v>142.67260576046</v>
-      </c>
-      <c r="P19" t="n">
-        <v>142.67260576046</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>142.67260576046</v>
-      </c>
-      <c r="R19" t="n">
-        <v>142.67260576046</v>
-      </c>
-      <c r="S19" t="n">
-        <v>18.56</v>
-      </c>
-      <c r="T19" t="n">
-        <v>39.14747915880486</v>
-      </c>
-      <c r="U19" t="n">
-        <v>115.4543117970915</v>
-      </c>
-      <c r="V19" t="n">
-        <v>143.9957046830374</v>
-      </c>
-      <c r="W19" t="n">
-        <v>145.6066229427149</v>
-      </c>
       <c r="X19" t="n">
-        <v>145.6066229427149</v>
+        <v>232.4891266316294</v>
       </c>
       <c r="Y19" t="n">
-        <v>145.6066229427149</v>
+        <v>172.4231136523745</v>
       </c>
     </row>
     <row r="20">
@@ -5719,58 +5719,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>363.8435906547704</v>
+        <v>373.2828729405136</v>
       </c>
       <c r="C20" t="n">
-        <v>363.8435906547704</v>
+        <v>373.2828729405136</v>
       </c>
       <c r="D20" t="n">
-        <v>363.8435906547704</v>
+        <v>373.2828729405136</v>
       </c>
       <c r="E20" t="n">
-        <v>363.8435906547704</v>
+        <v>373.2828729405136</v>
       </c>
       <c r="F20" t="n">
-        <v>185.167198020415</v>
+        <v>194.6064803061582</v>
       </c>
       <c r="G20" t="n">
-        <v>185.167198020415</v>
+        <v>18.56</v>
       </c>
       <c r="H20" t="n">
         <v>18.56</v>
       </c>
       <c r="I20" t="n">
-        <v>18.56</v>
+        <v>32.4163439355395</v>
       </c>
       <c r="J20" t="n">
-        <v>107.4981959781646</v>
+        <v>127.9639908713899</v>
       </c>
       <c r="K20" t="n">
-        <v>292.788675475652</v>
+        <v>313.2544703688773</v>
       </c>
       <c r="L20" t="n">
-        <v>522.4686754756519</v>
+        <v>542.9344703688773</v>
       </c>
       <c r="M20" t="n">
-        <v>522.4686754756519</v>
+        <v>542.9344703688773</v>
       </c>
       <c r="N20" t="n">
-        <v>522.4686754756519</v>
+        <v>542.9344703688773</v>
       </c>
       <c r="O20" t="n">
-        <v>698.3512792706672</v>
+        <v>718.8170741638927</v>
       </c>
       <c r="P20" t="n">
-        <v>907.5342051067745</v>
+        <v>928</v>
       </c>
       <c r="Q20" t="n">
-        <v>907.5342051067745</v>
+        <v>928</v>
       </c>
       <c r="R20" t="n">
         <v>928</v>
       </c>
       <c r="S20" t="n">
-        <v>693.6565656565656</v>
+        <v>928</v>
       </c>
       <c r="T20" t="n">
         <v>693.6565656565656</v>
@@ -5779,16 +5779,16 @@
         <v>693.6565656565656</v>
       </c>
       <c r="V20" t="n">
-        <v>459.3131313131312</v>
+        <v>607.6263072839479</v>
       </c>
       <c r="W20" t="n">
-        <v>459.3131313131312</v>
+        <v>607.6263072839479</v>
       </c>
       <c r="X20" t="n">
-        <v>363.8435906547704</v>
+        <v>607.6263072839479</v>
       </c>
       <c r="Y20" t="n">
-        <v>363.8435906547704</v>
+        <v>607.6263072839479</v>
       </c>
     </row>
     <row r="21">
@@ -5798,19 +5798,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>228.8642398472993</v>
+        <v>214.0319653565232</v>
       </c>
       <c r="C21" t="n">
-        <v>228.8642398472993</v>
+        <v>214.0319653565232</v>
       </c>
       <c r="D21" t="n">
-        <v>228.8642398472993</v>
+        <v>214.0319653565232</v>
       </c>
       <c r="E21" t="n">
-        <v>228.8642398472993</v>
+        <v>214.0319653565232</v>
       </c>
       <c r="F21" t="n">
-        <v>116.1003586979287</v>
+        <v>214.0319653565232</v>
       </c>
       <c r="G21" t="n">
         <v>116.1003586979287</v>
@@ -5819,28 +5819,28 @@
         <v>18.56</v>
       </c>
       <c r="I21" t="n">
-        <v>56.1585477788857</v>
+        <v>18.56</v>
       </c>
       <c r="J21" t="n">
-        <v>200.3997030904306</v>
+        <v>248.24</v>
       </c>
       <c r="K21" t="n">
-        <v>430.0797030904307</v>
+        <v>477.92</v>
       </c>
       <c r="L21" t="n">
-        <v>486.444756496091</v>
+        <v>534.2850534056604</v>
       </c>
       <c r="M21" t="n">
-        <v>528.7427260131439</v>
+        <v>576.5830229227132</v>
       </c>
       <c r="N21" t="n">
-        <v>528.7427260131439</v>
+        <v>758.5399110904731</v>
       </c>
       <c r="O21" t="n">
-        <v>574.3628193367983</v>
+        <v>804.1600044141276</v>
       </c>
       <c r="P21" t="n">
-        <v>774.1422143263673</v>
+        <v>848.5561717086601</v>
       </c>
       <c r="Q21" t="n">
         <v>928</v>
@@ -5855,19 +5855,19 @@
         <v>752.0559451776589</v>
       </c>
       <c r="U21" t="n">
-        <v>578.1584024429553</v>
+        <v>752.0559451776589</v>
       </c>
       <c r="V21" t="n">
-        <v>389.7637891181874</v>
+        <v>563.6613318528911</v>
       </c>
       <c r="W21" t="n">
-        <v>228.8642398472993</v>
+        <v>563.6613318528911</v>
       </c>
       <c r="X21" t="n">
-        <v>228.8642398472993</v>
+        <v>545.2925203186051</v>
       </c>
       <c r="Y21" t="n">
-        <v>228.8642398472993</v>
+        <v>372.1699013629137</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>65.90056407446244</v>
+        <v>185.2551449624971</v>
       </c>
       <c r="C22" t="n">
-        <v>65.90056407446244</v>
+        <v>140.0781281462904</v>
       </c>
       <c r="D22" t="n">
-        <v>30.08520152096339</v>
+        <v>81.96073617098179</v>
       </c>
       <c r="E22" t="n">
-        <v>30.08520152096339</v>
+        <v>81.96073617098179</v>
       </c>
       <c r="F22" t="n">
-        <v>30.08520152096339</v>
+        <v>35.10936650659599</v>
       </c>
       <c r="G22" t="n">
-        <v>30.08520152096339</v>
+        <v>18.56</v>
       </c>
       <c r="H22" t="n">
-        <v>35.13110668036096</v>
+        <v>23.60590515939757</v>
       </c>
       <c r="I22" t="n">
-        <v>105.6335056164439</v>
+        <v>94.10830409548048</v>
       </c>
       <c r="J22" t="n">
-        <v>335.3135056164439</v>
+        <v>323.7883040954805</v>
       </c>
       <c r="K22" t="n">
-        <v>351.3111395533123</v>
+        <v>339.7859380323489</v>
       </c>
       <c r="L22" t="n">
-        <v>252.9034343434344</v>
+        <v>339.7859380323489</v>
       </c>
       <c r="M22" t="n">
-        <v>252.9034343434344</v>
+        <v>339.7859380323489</v>
       </c>
       <c r="N22" t="n">
-        <v>252.9034343434344</v>
+        <v>137.5594773401724</v>
       </c>
       <c r="O22" t="n">
-        <v>252.9034343434344</v>
+        <v>137.5594773401724</v>
       </c>
       <c r="P22" t="n">
-        <v>252.9034343434344</v>
+        <v>137.5594773401724</v>
       </c>
       <c r="Q22" t="n">
-        <v>252.9034343434344</v>
+        <v>137.5594773401724</v>
       </c>
       <c r="R22" t="n">
-        <v>18.56</v>
+        <v>137.5594773401724</v>
       </c>
       <c r="S22" t="n">
-        <v>18.56</v>
+        <v>137.5594773401724</v>
       </c>
       <c r="T22" t="n">
-        <v>39.14747915880486</v>
+        <v>158.1469564989772</v>
       </c>
       <c r="U22" t="n">
-        <v>115.4543117970915</v>
+        <v>234.4537891372639</v>
       </c>
       <c r="V22" t="n">
-        <v>143.9957046830374</v>
+        <v>262.9951820232098</v>
       </c>
       <c r="W22" t="n">
-        <v>145.6066229427149</v>
+        <v>264.6061002828873</v>
       </c>
       <c r="X22" t="n">
-        <v>125.9665770537173</v>
+        <v>244.9660543938897</v>
       </c>
       <c r="Y22" t="n">
-        <v>65.90056407446244</v>
+        <v>244.9660543938897</v>
       </c>
     </row>
     <row r="23">
@@ -5956,19 +5956,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>459.3131313131312</v>
+        <v>771.204595585781</v>
       </c>
       <c r="C23" t="n">
-        <v>459.3131313131312</v>
+        <v>547.4929003908377</v>
       </c>
       <c r="D23" t="n">
-        <v>459.3131313131312</v>
+        <v>363.31193499705</v>
       </c>
       <c r="E23" t="n">
-        <v>281.1683943364962</v>
+        <v>185.167198020415</v>
       </c>
       <c r="F23" t="n">
-        <v>281.1683943364962</v>
+        <v>185.167198020415</v>
       </c>
       <c r="G23" t="n">
         <v>185.167198020415</v>
@@ -5980,25 +5980,25 @@
         <v>18.56</v>
       </c>
       <c r="J23" t="n">
-        <v>107.4981959781646</v>
+        <v>127.9639908713899</v>
       </c>
       <c r="K23" t="n">
-        <v>292.788675475652</v>
+        <v>313.2544703688773</v>
       </c>
       <c r="L23" t="n">
-        <v>522.4686754756519</v>
+        <v>542.9344703688773</v>
       </c>
       <c r="M23" t="n">
-        <v>522.4686754756519</v>
+        <v>542.9344703688773</v>
       </c>
       <c r="N23" t="n">
-        <v>522.4686754756519</v>
+        <v>542.9344703688773</v>
       </c>
       <c r="O23" t="n">
-        <v>698.3512792706672</v>
+        <v>718.8170741638927</v>
       </c>
       <c r="P23" t="n">
-        <v>907.5342051067745</v>
+        <v>928</v>
       </c>
       <c r="Q23" t="n">
         <v>928</v>
@@ -6007,25 +6007,25 @@
         <v>928</v>
       </c>
       <c r="S23" t="n">
-        <v>693.6565656565656</v>
+        <v>928</v>
       </c>
       <c r="T23" t="n">
-        <v>693.6565656565656</v>
+        <v>771.204595585781</v>
       </c>
       <c r="U23" t="n">
-        <v>693.6565656565656</v>
+        <v>771.204595585781</v>
       </c>
       <c r="V23" t="n">
-        <v>693.6565656565656</v>
+        <v>771.204595585781</v>
       </c>
       <c r="W23" t="n">
-        <v>693.6565656565656</v>
+        <v>771.204595585781</v>
       </c>
       <c r="X23" t="n">
-        <v>459.3131313131312</v>
+        <v>771.204595585781</v>
       </c>
       <c r="Y23" t="n">
-        <v>459.3131313131312</v>
+        <v>771.204595585781</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>386.9174158394937</v>
+        <v>366.3751159377589</v>
       </c>
       <c r="C24" t="n">
-        <v>252.4730598339187</v>
+        <v>231.9307599321839</v>
       </c>
       <c r="D24" t="n">
-        <v>131.3238811493706</v>
+        <v>231.9307599321839</v>
       </c>
       <c r="E24" t="n">
-        <v>131.3238811493706</v>
+        <v>116.1003586979287</v>
       </c>
       <c r="F24" t="n">
-        <v>18.56</v>
+        <v>116.1003586979287</v>
       </c>
       <c r="G24" t="n">
-        <v>18.56</v>
+        <v>116.1003586979287</v>
       </c>
       <c r="H24" t="n">
         <v>18.56</v>
@@ -6062,49 +6062,49 @@
         <v>236.7283083154666</v>
       </c>
       <c r="K24" t="n">
-        <v>466.4083083154666</v>
+        <v>258.8513065215043</v>
       </c>
       <c r="L24" t="n">
-        <v>522.773361721127</v>
+        <v>488.5313065215043</v>
       </c>
       <c r="M24" t="n">
-        <v>522.773361721127</v>
+        <v>488.5313065215043</v>
       </c>
       <c r="N24" t="n">
-        <v>522.773361721127</v>
+        <v>488.5313065215043</v>
       </c>
       <c r="O24" t="n">
-        <v>568.3934550447814</v>
+        <v>706.366502683761</v>
       </c>
       <c r="P24" t="n">
-        <v>798.0734550447814</v>
+        <v>791.2446577164653</v>
       </c>
       <c r="Q24" t="n">
         <v>928</v>
       </c>
       <c r="R24" t="n">
-        <v>925.1536267213062</v>
+        <v>928</v>
       </c>
       <c r="S24" t="n">
-        <v>925.1536267213062</v>
+        <v>928</v>
       </c>
       <c r="T24" t="n">
-        <v>749.2095718989652</v>
+        <v>928</v>
       </c>
       <c r="U24" t="n">
-        <v>575.3120291642616</v>
+        <v>928</v>
       </c>
       <c r="V24" t="n">
-        <v>386.9174158394937</v>
+        <v>739.6053866752321</v>
       </c>
       <c r="W24" t="n">
-        <v>386.9174158394937</v>
+        <v>739.6053866752321</v>
       </c>
       <c r="X24" t="n">
-        <v>386.9174158394937</v>
+        <v>545.8046397606993</v>
       </c>
       <c r="Y24" t="n">
-        <v>386.9174158394937</v>
+        <v>372.682020805008</v>
       </c>
     </row>
     <row r="25">
@@ -6114,13 +6114,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>177.0448271315697</v>
+        <v>123.5287616396944</v>
       </c>
       <c r="C25" t="n">
-        <v>177.0448271315697</v>
+        <v>123.5287616396944</v>
       </c>
       <c r="D25" t="n">
-        <v>118.9274351562611</v>
+        <v>65.41136966438579</v>
       </c>
       <c r="E25" t="n">
         <v>65.41136966438579</v>
@@ -6156,34 +6156,34 @@
         <v>339.7859380323489</v>
       </c>
       <c r="P25" t="n">
+        <v>339.7859380323489</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>339.7859380323489</v>
+      </c>
+      <c r="R25" t="n">
         <v>105.4425036889145</v>
       </c>
-      <c r="Q25" t="n">
-        <v>49.99820418885476</v>
-      </c>
-      <c r="R25" t="n">
-        <v>49.99820418885476</v>
-      </c>
       <c r="S25" t="n">
-        <v>49.99820418885476</v>
+        <v>105.4425036889145</v>
       </c>
       <c r="T25" t="n">
-        <v>70.58568334765963</v>
+        <v>126.0299828477194</v>
       </c>
       <c r="U25" t="n">
-        <v>146.8925159859463</v>
+        <v>202.3368154860061</v>
       </c>
       <c r="V25" t="n">
-        <v>175.4339088718922</v>
+        <v>230.878208371952</v>
       </c>
       <c r="W25" t="n">
-        <v>177.0448271315697</v>
+        <v>232.4891266316295</v>
       </c>
       <c r="X25" t="n">
-        <v>177.0448271315697</v>
+        <v>232.4891266316295</v>
       </c>
       <c r="Y25" t="n">
-        <v>177.0448271315697</v>
+        <v>172.4231136523746</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14.16</v>
+        <v>550.5236363636423</v>
       </c>
       <c r="C26" t="n">
-        <v>14.16</v>
+        <v>371.735757575762</v>
       </c>
       <c r="D26" t="n">
-        <v>14.16</v>
+        <v>192.9478787878818</v>
       </c>
       <c r="E26" t="n">
-        <v>14.16</v>
+        <v>192.9478787878818</v>
       </c>
       <c r="F26" t="n">
-        <v>14.16</v>
+        <v>192.9478787878818</v>
       </c>
       <c r="G26" t="n">
-        <v>14.16</v>
+        <v>192.9478787878818</v>
       </c>
       <c r="H26" t="n">
         <v>14.16</v>
@@ -6226,7 +6226,7 @@
         <v>453.5581959781646</v>
       </c>
       <c r="M26" t="n">
-        <v>378.9069325863513</v>
+        <v>360.2784734576783</v>
       </c>
       <c r="N26" t="n">
         <v>357.54</v>
@@ -6244,25 +6244,25 @@
         <v>708</v>
       </c>
       <c r="S26" t="n">
-        <v>529.2121212121187</v>
+        <v>708</v>
       </c>
       <c r="T26" t="n">
-        <v>371.7357575757602</v>
+        <v>708</v>
       </c>
       <c r="U26" t="n">
-        <v>371.7357575757602</v>
+        <v>708</v>
       </c>
       <c r="V26" t="n">
-        <v>371.7357575757602</v>
+        <v>708</v>
       </c>
       <c r="W26" t="n">
-        <v>192.9478787878802</v>
+        <v>550.5236363636423</v>
       </c>
       <c r="X26" t="n">
-        <v>192.9478787878802</v>
+        <v>550.5236363636423</v>
       </c>
       <c r="Y26" t="n">
-        <v>14.16</v>
+        <v>550.5236363636423</v>
       </c>
     </row>
     <row r="27">
@@ -6272,46 +6272,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>708</v>
+        <v>296.7579895630626</v>
       </c>
       <c r="C27" t="n">
-        <v>640.1835072327779</v>
+        <v>146.1520173958714</v>
       </c>
       <c r="D27" t="n">
-        <v>502.8727123866136</v>
+        <v>146.1520173958714</v>
       </c>
       <c r="E27" t="n">
-        <v>370.8806949907422</v>
+        <v>14.16</v>
       </c>
       <c r="F27" t="n">
-        <v>241.9551976797555</v>
+        <v>14.16</v>
       </c>
       <c r="G27" t="n">
-        <v>127.8619748595449</v>
+        <v>14.16</v>
       </c>
       <c r="H27" t="n">
         <v>14.16</v>
       </c>
       <c r="I27" t="n">
-        <v>35.91854777888571</v>
+        <v>14.16</v>
       </c>
       <c r="J27" t="n">
-        <v>35.91854777888571</v>
+        <v>142.8468176564618</v>
       </c>
       <c r="K27" t="n">
-        <v>211.1485477788857</v>
+        <v>318.0768176564618</v>
       </c>
       <c r="L27" t="n">
-        <v>375.635003196446</v>
+        <v>488.3738327054674</v>
       </c>
       <c r="M27" t="n">
-        <v>375.635003196446</v>
+        <v>488.3738327054674</v>
       </c>
       <c r="N27" t="n">
-        <v>375.635003196446</v>
+        <v>488.3738327054674</v>
       </c>
       <c r="O27" t="n">
-        <v>550.865003196446</v>
+        <v>663.6038327054674</v>
       </c>
       <c r="P27" t="n">
         <v>708</v>
@@ -6326,22 +6326,22 @@
         <v>708</v>
       </c>
       <c r="T27" t="n">
-        <v>708</v>
+        <v>654.3337471388227</v>
       </c>
       <c r="U27" t="n">
-        <v>708</v>
+        <v>654.3337471388227</v>
       </c>
       <c r="V27" t="n">
-        <v>708</v>
+        <v>654.3337471388227</v>
       </c>
       <c r="W27" t="n">
-        <v>708</v>
+        <v>654.3337471388227</v>
       </c>
       <c r="X27" t="n">
-        <v>708</v>
+        <v>475.5458683509426</v>
       </c>
       <c r="Y27" t="n">
-        <v>708</v>
+        <v>296.7579895630626</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>182.2358601605407</v>
+        <v>92.07570468303747</v>
       </c>
       <c r="C28" t="n">
-        <v>120.8972271827178</v>
+        <v>92.07570468303747</v>
       </c>
       <c r="D28" t="n">
-        <v>120.8972271827178</v>
+        <v>92.07570468303747</v>
       </c>
       <c r="E28" t="n">
-        <v>120.8972271827178</v>
+        <v>92.07570468303747</v>
       </c>
       <c r="F28" t="n">
-        <v>57.88424135671581</v>
+        <v>92.07570468303747</v>
       </c>
       <c r="G28" t="n">
-        <v>25.17325868850365</v>
+        <v>92.07570468303747</v>
       </c>
       <c r="H28" t="n">
+        <v>92.07570468303747</v>
+      </c>
+      <c r="I28" t="n">
+        <v>146.7381036191204</v>
+      </c>
+      <c r="J28" t="n">
+        <v>321.9681036191204</v>
+      </c>
+      <c r="K28" t="n">
+        <v>322.1257375559887</v>
+      </c>
+      <c r="L28" t="n">
+        <v>322.1257375559887</v>
+      </c>
+      <c r="M28" t="n">
+        <v>322.1257375559887</v>
+      </c>
+      <c r="N28" t="n">
+        <v>322.1257375559887</v>
+      </c>
+      <c r="O28" t="n">
+        <v>143.3378587681099</v>
+      </c>
+      <c r="P28" t="n">
+        <v>143.3378587681099</v>
+      </c>
+      <c r="Q28" t="n">
         <v>14.16</v>
       </c>
-      <c r="I28" t="n">
-        <v>68.82239893608291</v>
-      </c>
-      <c r="J28" t="n">
-        <v>244.0523989360829</v>
-      </c>
-      <c r="K28" t="n">
-        <v>244.2100328729513</v>
-      </c>
-      <c r="L28" t="n">
-        <v>244.2100328729513</v>
-      </c>
-      <c r="M28" t="n">
-        <v>244.2100328729513</v>
-      </c>
-      <c r="N28" t="n">
-        <v>244.2100328729513</v>
-      </c>
-      <c r="O28" t="n">
-        <v>244.2100328729513</v>
-      </c>
-      <c r="P28" t="n">
-        <v>244.2100328729513</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>195.0657743544447</v>
-      </c>
       <c r="R28" t="n">
-        <v>195.0657743544447</v>
+        <v>14.16</v>
       </c>
       <c r="S28" t="n">
-        <v>195.0657743544447</v>
+        <v>14.16</v>
       </c>
       <c r="T28" t="n">
-        <v>199.8132535132495</v>
+        <v>18.90747915880486</v>
       </c>
       <c r="U28" t="n">
-        <v>260.2800861515362</v>
+        <v>79.37431179709151</v>
       </c>
       <c r="V28" t="n">
-        <v>272.9814790374821</v>
+        <v>92.07570468303747</v>
       </c>
       <c r="W28" t="n">
-        <v>258.4634893014118</v>
+        <v>92.07570468303747</v>
       </c>
       <c r="X28" t="n">
-        <v>258.4634893014118</v>
+        <v>92.07570468303747</v>
       </c>
       <c r="Y28" t="n">
-        <v>182.2358601605407</v>
+        <v>92.07570468303747</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>350.4242424242424</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="C29" t="n">
-        <v>350.4242424242424</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="D29" t="n">
-        <v>350.4242424242424</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="E29" t="n">
-        <v>350.4242424242424</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="F29" t="n">
-        <v>350.4242424242424</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="G29" t="n">
-        <v>171.6363636363636</v>
+        <v>14.16</v>
       </c>
       <c r="H29" t="n">
         <v>14.16</v>
@@ -6481,19 +6481,19 @@
         <v>708</v>
       </c>
       <c r="S29" t="n">
-        <v>529.2121212121212</v>
+        <v>708</v>
       </c>
       <c r="T29" t="n">
-        <v>529.2121212121212</v>
+        <v>708</v>
       </c>
       <c r="U29" t="n">
         <v>529.2121212121212</v>
       </c>
       <c r="V29" t="n">
-        <v>529.2121212121212</v>
+        <v>350.4242424242424</v>
       </c>
       <c r="W29" t="n">
-        <v>529.2121212121212</v>
+        <v>350.4242424242424</v>
       </c>
       <c r="X29" t="n">
         <v>350.4242424242424</v>
@@ -6509,43 +6509,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373.9472150756268</v>
+        <v>350.4242424242424</v>
       </c>
       <c r="C30" t="n">
-        <v>373.9472150756268</v>
+        <v>350.4242424242424</v>
       </c>
       <c r="D30" t="n">
-        <v>373.9472150756268</v>
+        <v>213.1134475780781</v>
       </c>
       <c r="E30" t="n">
-        <v>241.9551976797555</v>
+        <v>81.12143018220678</v>
       </c>
       <c r="F30" t="n">
-        <v>241.9551976797555</v>
+        <v>81.12143018220678</v>
       </c>
       <c r="G30" t="n">
-        <v>127.8619748595449</v>
+        <v>14.16</v>
       </c>
       <c r="H30" t="n">
         <v>14.16</v>
       </c>
       <c r="I30" t="n">
-        <v>35.42002875650936</v>
+        <v>14.16</v>
       </c>
       <c r="J30" t="n">
-        <v>210.6500287565094</v>
+        <v>189.39</v>
       </c>
       <c r="K30" t="n">
-        <v>246.6121803835083</v>
+        <v>364.62</v>
       </c>
       <c r="L30" t="n">
-        <v>421.8421803835083</v>
+        <v>420.9850534056604</v>
       </c>
       <c r="M30" t="n">
-        <v>421.8421803835083</v>
+        <v>447.4430229227132</v>
       </c>
       <c r="N30" t="n">
-        <v>487.1499066763456</v>
+        <v>447.4430229227132</v>
       </c>
       <c r="O30" t="n">
         <v>532.77</v>
@@ -6566,19 +6566,19 @@
         <v>708</v>
       </c>
       <c r="U30" t="n">
-        <v>552.7350938635057</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="V30" t="n">
-        <v>373.9472150756268</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="W30" t="n">
-        <v>373.9472150756268</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="X30" t="n">
-        <v>373.9472150756268</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="Y30" t="n">
-        <v>373.9472150756268</v>
+        <v>350.4242424242424</v>
       </c>
     </row>
     <row r="31">
@@ -6588,28 +6588,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>99.45226682542838</v>
+        <v>143.3378587681099</v>
       </c>
       <c r="C31" t="n">
-        <v>99.45226682542838</v>
+        <v>81.99922579028703</v>
       </c>
       <c r="D31" t="n">
-        <v>25.17325868850365</v>
+        <v>81.99922579028703</v>
       </c>
       <c r="E31" t="n">
-        <v>25.17325868850365</v>
+        <v>81.99922579028703</v>
       </c>
       <c r="F31" t="n">
-        <v>25.17325868850365</v>
+        <v>18.98623996428507</v>
       </c>
       <c r="G31" t="n">
-        <v>25.17325868850365</v>
+        <v>14.16</v>
       </c>
       <c r="H31" t="n">
         <v>14.16</v>
       </c>
       <c r="I31" t="n">
-        <v>68.82239893608291</v>
+        <v>68.82239893608292</v>
       </c>
       <c r="J31" t="n">
         <v>244.0523989360829</v>
@@ -6618,46 +6618,46 @@
         <v>244.2100328729513</v>
       </c>
       <c r="L31" t="n">
-        <v>129.6407115014572</v>
+        <v>244.2100328729513</v>
       </c>
       <c r="M31" t="n">
-        <v>129.6407115014572</v>
+        <v>244.2100328729513</v>
       </c>
       <c r="N31" t="n">
-        <v>129.6407115014572</v>
+        <v>244.2100328729513</v>
       </c>
       <c r="O31" t="n">
-        <v>129.6407115014572</v>
+        <v>244.2100328729513</v>
       </c>
       <c r="P31" t="n">
-        <v>129.6407115014572</v>
+        <v>244.2100328729513</v>
       </c>
       <c r="Q31" t="n">
-        <v>129.6407115014572</v>
+        <v>65.42215408507246</v>
       </c>
       <c r="R31" t="n">
-        <v>129.6407115014572</v>
+        <v>65.42215408507246</v>
       </c>
       <c r="S31" t="n">
-        <v>129.6407115014572</v>
+        <v>65.42215408507246</v>
       </c>
       <c r="T31" t="n">
-        <v>134.388190660262</v>
+        <v>70.16963324387731</v>
       </c>
       <c r="U31" t="n">
-        <v>194.8550232985486</v>
+        <v>130.6364658821639</v>
       </c>
       <c r="V31" t="n">
-        <v>207.5564161844946</v>
+        <v>143.3378587681099</v>
       </c>
       <c r="W31" t="n">
-        <v>207.5564161844946</v>
+        <v>143.3378587681099</v>
       </c>
       <c r="X31" t="n">
-        <v>207.5564161844946</v>
+        <v>143.3378587681099</v>
       </c>
       <c r="Y31" t="n">
-        <v>175.3247924184371</v>
+        <v>143.3378587681099</v>
       </c>
     </row>
     <row r="32">
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>350.4242424242424</v>
+        <v>472.3916213231973</v>
       </c>
       <c r="C32" t="n">
-        <v>350.4242424242424</v>
+        <v>293.6037425353185</v>
       </c>
       <c r="D32" t="n">
-        <v>350.4242424242424</v>
+        <v>293.6037425353185</v>
       </c>
       <c r="E32" t="n">
-        <v>209.6532428213448</v>
+        <v>152.8327429324208</v>
       </c>
       <c r="F32" t="n">
-        <v>209.6532428213448</v>
+        <v>152.8327429324208</v>
       </c>
       <c r="G32" t="n">
-        <v>70.98049988892396</v>
+        <v>14.16</v>
       </c>
       <c r="H32" t="n">
         <v>14.16</v>
@@ -6718,13 +6718,13 @@
         <v>708</v>
       </c>
       <c r="S32" t="n">
-        <v>529.2121212121212</v>
+        <v>708</v>
       </c>
       <c r="T32" t="n">
-        <v>529.2121212121212</v>
+        <v>708</v>
       </c>
       <c r="U32" t="n">
-        <v>529.2121212121212</v>
+        <v>708</v>
       </c>
       <c r="V32" t="n">
         <v>529.2121212121212</v>
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>111.2306186318377</v>
+        <v>134.8844906090484</v>
       </c>
       <c r="C33" t="n">
-        <v>14.16</v>
+        <v>134.8844906090484</v>
       </c>
       <c r="D33" t="n">
-        <v>14.16</v>
+        <v>134.8844906090484</v>
       </c>
       <c r="E33" t="n">
-        <v>14.16</v>
+        <v>134.8844906090484</v>
       </c>
       <c r="F33" t="n">
-        <v>14.16</v>
+        <v>134.8844906090484</v>
       </c>
       <c r="G33" t="n">
-        <v>14.16</v>
+        <v>74.32662132419135</v>
       </c>
       <c r="H33" t="n">
         <v>14.16</v>
       </c>
       <c r="I33" t="n">
-        <v>70.17074117577526</v>
+        <v>14.16</v>
       </c>
       <c r="J33" t="n">
-        <v>70.17074117577526</v>
+        <v>20.74688265544506</v>
       </c>
       <c r="K33" t="n">
-        <v>92.29373938181303</v>
+        <v>195.9768826554451</v>
       </c>
       <c r="L33" t="n">
-        <v>267.523739381813</v>
+        <v>314.9884904219327</v>
       </c>
       <c r="M33" t="n">
-        <v>267.523739381813</v>
+        <v>314.9884904219327</v>
       </c>
       <c r="N33" t="n">
-        <v>442.753739381813</v>
+        <v>314.9884904219327</v>
       </c>
       <c r="O33" t="n">
-        <v>488.3738327054675</v>
+        <v>490.2184904219327</v>
       </c>
       <c r="P33" t="n">
-        <v>532.77</v>
+        <v>534.6146577164652</v>
       </c>
       <c r="Q33" t="n">
         <v>708</v>
       </c>
       <c r="R33" t="n">
-        <v>542.751750982203</v>
+        <v>708</v>
       </c>
       <c r="S33" t="n">
-        <v>542.751750982203</v>
+        <v>708</v>
       </c>
       <c r="T33" t="n">
-        <v>404.1814335335994</v>
+        <v>708</v>
       </c>
       <c r="U33" t="n">
-        <v>267.6576281726332</v>
+        <v>578.0812576828283</v>
       </c>
       <c r="V33" t="n">
-        <v>267.6576281726332</v>
+        <v>427.0603817317979</v>
       </c>
       <c r="W33" t="n">
-        <v>267.6576281726332</v>
+        <v>427.0603817317979</v>
       </c>
       <c r="X33" t="n">
-        <v>111.2306186318377</v>
+        <v>270.6333721910023</v>
       </c>
       <c r="Y33" t="n">
-        <v>111.2306186318377</v>
+        <v>134.8844906090484</v>
       </c>
     </row>
     <row r="34">
@@ -6855,19 +6855,19 @@
         <v>602.9869757701429</v>
       </c>
       <c r="L34" t="n">
-        <v>541.9530079340022</v>
+        <v>602.9869757701429</v>
       </c>
       <c r="M34" t="n">
-        <v>541.9530079340022</v>
+        <v>449.2762571817086</v>
       </c>
       <c r="N34" t="n">
-        <v>363.1651291461234</v>
+        <v>449.2762571817086</v>
       </c>
       <c r="O34" t="n">
-        <v>184.3772503582446</v>
+        <v>270.4883783938298</v>
       </c>
       <c r="P34" t="n">
-        <v>14.16</v>
+        <v>91.70049960595099</v>
       </c>
       <c r="Q34" t="n">
         <v>14.16</v>
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>282.0662035790984</v>
+        <v>440.9426262130892</v>
       </c>
       <c r="C35" t="n">
-        <v>282.0662035790984</v>
+        <v>440.9426262130892</v>
       </c>
       <c r="D35" t="n">
-        <v>282.0662035790984</v>
+        <v>294.1353981930389</v>
       </c>
       <c r="E35" t="n">
-        <v>282.0662035790984</v>
+        <v>294.1353981930389</v>
       </c>
       <c r="F35" t="n">
-        <v>282.0662035790984</v>
+        <v>152.8327429324208</v>
       </c>
       <c r="G35" t="n">
-        <v>143.3934606466776</v>
+        <v>14.16</v>
       </c>
       <c r="H35" t="n">
         <v>14.16</v>
@@ -6937,7 +6937,7 @@
         <v>453.5581959781646</v>
       </c>
       <c r="M35" t="n">
-        <v>357.54</v>
+        <v>453.5581959781646</v>
       </c>
       <c r="N35" t="n">
         <v>357.54</v>
@@ -6955,25 +6955,25 @@
         <v>708</v>
       </c>
       <c r="S35" t="n">
-        <v>639.6419611548561</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="T35" t="n">
-        <v>639.6419611548561</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="U35" t="n">
-        <v>460.8540823669773</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="V35" t="n">
-        <v>460.8540823669773</v>
+        <v>440.9426262130892</v>
       </c>
       <c r="W35" t="n">
-        <v>282.0662035790984</v>
+        <v>440.9426262130892</v>
       </c>
       <c r="X35" t="n">
-        <v>282.0662035790984</v>
+        <v>440.9426262130892</v>
       </c>
       <c r="Y35" t="n">
-        <v>282.0662035790984</v>
+        <v>440.9426262130892</v>
       </c>
     </row>
     <row r="36">
@@ -6983,49 +6983,49 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>391.1206943273299</v>
+        <v>150.1080130604902</v>
       </c>
       <c r="C36" t="n">
-        <v>294.0500756954923</v>
+        <v>150.1080130604902</v>
       </c>
       <c r="D36" t="n">
-        <v>210.2746343846816</v>
+        <v>150.1080130604902</v>
       </c>
       <c r="E36" t="n">
-        <v>210.2746343846816</v>
+        <v>150.1080130604902</v>
       </c>
       <c r="F36" t="n">
-        <v>134.8844906090484</v>
+        <v>74.71786928485704</v>
       </c>
       <c r="G36" t="n">
-        <v>74.32662132419135</v>
+        <v>14.16</v>
       </c>
       <c r="H36" t="n">
         <v>14.16</v>
       </c>
       <c r="I36" t="n">
-        <v>88.38854777888569</v>
+        <v>14.16</v>
       </c>
       <c r="J36" t="n">
-        <v>88.38854777888569</v>
+        <v>14.16</v>
       </c>
       <c r="K36" t="n">
-        <v>211.1586859761526</v>
+        <v>36.28299820603777</v>
       </c>
       <c r="L36" t="n">
-        <v>267.523739381813</v>
+        <v>211.5129982060378</v>
       </c>
       <c r="M36" t="n">
-        <v>442.753739381813</v>
+        <v>386.7429982060378</v>
       </c>
       <c r="N36" t="n">
-        <v>442.753739381813</v>
+        <v>504.520724498875</v>
       </c>
       <c r="O36" t="n">
-        <v>488.3738327054675</v>
+        <v>550.1408178225295</v>
       </c>
       <c r="P36" t="n">
-        <v>532.77</v>
+        <v>638.7933567040427</v>
       </c>
       <c r="Q36" t="n">
         <v>708</v>
@@ -7037,22 +7037,22 @@
         <v>708</v>
       </c>
       <c r="T36" t="n">
-        <v>708</v>
+        <v>569.4296825513964</v>
       </c>
       <c r="U36" t="n">
-        <v>708</v>
+        <v>563.0481028158929</v>
       </c>
       <c r="V36" t="n">
-        <v>708</v>
+        <v>563.0481028158929</v>
       </c>
       <c r="W36" t="n">
-        <v>668.3119025007786</v>
+        <v>563.0481028158929</v>
       </c>
       <c r="X36" t="n">
-        <v>511.8848929599831</v>
+        <v>406.6210932750973</v>
       </c>
       <c r="Y36" t="n">
-        <v>511.8848929599831</v>
+        <v>270.8722116931434</v>
       </c>
     </row>
     <row r="37">
@@ -7074,43 +7074,43 @@
         <v>215.3887041415572</v>
       </c>
       <c r="F37" t="n">
-        <v>215.3887041415572</v>
+        <v>205.9110718509087</v>
       </c>
       <c r="G37" t="n">
-        <v>235.7986700284424</v>
+        <v>226.321037737794</v>
       </c>
       <c r="H37" t="n">
-        <v>277.4745751878399</v>
+        <v>267.9969428971916</v>
       </c>
       <c r="I37" t="n">
-        <v>384.6069741239229</v>
+        <v>375.1293418332745</v>
       </c>
       <c r="J37" t="n">
-        <v>559.8369741239229</v>
+        <v>550.3593418332745</v>
       </c>
       <c r="K37" t="n">
-        <v>612.4646080607913</v>
+        <v>602.9869757701429</v>
       </c>
       <c r="L37" t="n">
-        <v>551.4306402246507</v>
+        <v>602.9869757701429</v>
       </c>
       <c r="M37" t="n">
-        <v>551.4306402246507</v>
+        <v>602.9869757701429</v>
       </c>
       <c r="N37" t="n">
-        <v>551.4306402246507</v>
+        <v>424.1990969822641</v>
       </c>
       <c r="O37" t="n">
-        <v>551.4306402246507</v>
+        <v>371.7357575757576</v>
       </c>
       <c r="P37" t="n">
-        <v>372.6427614367719</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="Q37" t="n">
-        <v>193.8548826488931</v>
+        <v>14.16</v>
       </c>
       <c r="R37" t="n">
-        <v>100.8988683867227</v>
+        <v>14.16</v>
       </c>
       <c r="S37" t="n">
         <v>14.16</v>
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14.16</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="C38" t="n">
-        <v>14.16</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="D38" t="n">
-        <v>14.16</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="E38" t="n">
-        <v>14.16</v>
+        <v>30.86536403346599</v>
       </c>
       <c r="F38" t="n">
-        <v>14.16</v>
+        <v>30.86536403346599</v>
       </c>
       <c r="G38" t="n">
-        <v>14.16</v>
+        <v>30.86536403346599</v>
       </c>
       <c r="H38" t="n">
         <v>14.16</v>
@@ -7174,7 +7174,7 @@
         <v>453.5581959781646</v>
       </c>
       <c r="M38" t="n">
-        <v>453.5581959781646</v>
+        <v>432.4422861217048</v>
       </c>
       <c r="N38" t="n">
         <v>357.54</v>
@@ -7192,25 +7192,25 @@
         <v>708</v>
       </c>
       <c r="S38" t="n">
-        <v>708</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="T38" t="n">
-        <v>708</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="U38" t="n">
-        <v>529.2121212121212</v>
+        <v>350.4242424242424</v>
       </c>
       <c r="V38" t="n">
-        <v>350.4242424242424</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="W38" t="n">
-        <v>192.9478787878788</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="X38" t="n">
-        <v>14.16</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="Y38" t="n">
-        <v>14.16</v>
+        <v>171.6363636363636</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>391.1206943273299</v>
+        <v>270.3962037182816</v>
       </c>
       <c r="C39" t="n">
-        <v>294.0500756954923</v>
+        <v>173.3255850864439</v>
       </c>
       <c r="D39" t="n">
-        <v>210.2746343846816</v>
+        <v>89.5501437756332</v>
       </c>
       <c r="E39" t="n">
-        <v>210.2746343846816</v>
+        <v>89.5501437756332</v>
       </c>
       <c r="F39" t="n">
-        <v>134.8844906090484</v>
+        <v>14.16</v>
       </c>
       <c r="G39" t="n">
-        <v>74.32662132419135</v>
+        <v>14.16</v>
       </c>
       <c r="H39" t="n">
         <v>14.16</v>
       </c>
       <c r="I39" t="n">
-        <v>14.16</v>
+        <v>72.90444481736419</v>
       </c>
       <c r="J39" t="n">
-        <v>14.16</v>
+        <v>72.90444481736419</v>
       </c>
       <c r="K39" t="n">
-        <v>93.38095968331544</v>
+        <v>95.02744302340196</v>
       </c>
       <c r="L39" t="n">
-        <v>149.7460130889758</v>
+        <v>270.2574430234019</v>
       </c>
       <c r="M39" t="n">
-        <v>324.9760130889758</v>
+        <v>445.4874430234019</v>
       </c>
       <c r="N39" t="n">
-        <v>442.753739381813</v>
+        <v>488.3738327054674</v>
       </c>
       <c r="O39" t="n">
-        <v>488.3738327054675</v>
+        <v>663.6038327054674</v>
       </c>
       <c r="P39" t="n">
-        <v>532.77</v>
+        <v>708</v>
       </c>
       <c r="Q39" t="n">
         <v>708</v>
       </c>
       <c r="R39" t="n">
-        <v>650.4552104085867</v>
+        <v>708</v>
       </c>
       <c r="S39" t="n">
-        <v>650.4552104085867</v>
+        <v>708</v>
       </c>
       <c r="T39" t="n">
-        <v>511.8848929599831</v>
+        <v>708</v>
       </c>
       <c r="U39" t="n">
-        <v>511.8848929599831</v>
+        <v>571.4761946390338</v>
       </c>
       <c r="V39" t="n">
-        <v>511.8848929599831</v>
+        <v>420.4553186880033</v>
       </c>
       <c r="W39" t="n">
-        <v>511.8848929599831</v>
+        <v>420.4553186880033</v>
       </c>
       <c r="X39" t="n">
-        <v>511.8848929599831</v>
+        <v>406.1450853002356</v>
       </c>
       <c r="Y39" t="n">
-        <v>511.8848929599831</v>
+        <v>270.3962037182816</v>
       </c>
     </row>
     <row r="40">
@@ -7329,22 +7329,22 @@
         <v>602.9869757701429</v>
       </c>
       <c r="L40" t="n">
-        <v>541.9530079340022</v>
+        <v>602.9869757701429</v>
       </c>
       <c r="M40" t="n">
-        <v>541.9530079340022</v>
+        <v>602.9869757701429</v>
       </c>
       <c r="N40" t="n">
-        <v>541.9530079340022</v>
+        <v>602.9869757701429</v>
       </c>
       <c r="O40" t="n">
-        <v>363.1651291461234</v>
+        <v>458.4746259624803</v>
       </c>
       <c r="P40" t="n">
-        <v>184.3772503582446</v>
+        <v>279.6867471746015</v>
       </c>
       <c r="Q40" t="n">
-        <v>100.8988683867227</v>
+        <v>279.6867471746015</v>
       </c>
       <c r="R40" t="n">
         <v>100.8988683867227</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>411.4899770410347</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="C41" t="n">
-        <v>411.4899770410347</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="D41" t="n">
-        <v>411.4899770410347</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="E41" t="n">
-        <v>232.7020982531559</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="F41" t="n">
-        <v>232.7020982531559</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="G41" t="n">
-        <v>53.91421946527709</v>
+        <v>171.6363636363636</v>
       </c>
       <c r="H41" t="n">
         <v>53.91421946527709</v>
@@ -7411,7 +7411,7 @@
         <v>453.5581959781646</v>
       </c>
       <c r="M41" t="n">
-        <v>453.5581959781646</v>
+        <v>357.54</v>
       </c>
       <c r="N41" t="n">
         <v>357.54</v>
@@ -7426,28 +7426,28 @@
         <v>708</v>
       </c>
       <c r="R41" t="n">
-        <v>602.491431060197</v>
+        <v>708</v>
       </c>
       <c r="S41" t="n">
-        <v>423.7035522723182</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="T41" t="n">
-        <v>423.7035522723182</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="U41" t="n">
-        <v>411.4899770410347</v>
+        <v>529.2121212121212</v>
       </c>
       <c r="V41" t="n">
-        <v>411.4899770410347</v>
+        <v>350.4242424242424</v>
       </c>
       <c r="W41" t="n">
-        <v>411.4899770410347</v>
+        <v>350.4242424242424</v>
       </c>
       <c r="X41" t="n">
-        <v>411.4899770410347</v>
+        <v>350.4242424242424</v>
       </c>
       <c r="Y41" t="n">
-        <v>411.4899770410347</v>
+        <v>350.4242424242424</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>151.5556251618348</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="C42" t="n">
-        <v>151.5556251618348</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="D42" t="n">
-        <v>151.5556251618348</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="E42" t="n">
-        <v>151.5556251618348</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="F42" t="n">
-        <v>151.5556251618348</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="G42" t="n">
-        <v>151.5556251618348</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="H42" t="n">
-        <v>151.5556251618348</v>
+        <v>14.16</v>
       </c>
       <c r="I42" t="n">
         <v>14.16</v>
@@ -7484,16 +7484,16 @@
         <v>189.39</v>
       </c>
       <c r="K42" t="n">
-        <v>264.9729982060377</v>
+        <v>211.5129982060378</v>
       </c>
       <c r="L42" t="n">
-        <v>321.3380516116981</v>
+        <v>267.8780516116981</v>
       </c>
       <c r="M42" t="n">
-        <v>496.5680516116981</v>
+        <v>375.8503629606613</v>
       </c>
       <c r="N42" t="n">
-        <v>511.0637393818131</v>
+        <v>551.0803629606613</v>
       </c>
       <c r="O42" t="n">
         <v>610.1438327054675</v>
@@ -7502,31 +7502,31 @@
         <v>708</v>
       </c>
       <c r="Q42" t="n">
-        <v>689.2241461826678</v>
+        <v>708</v>
       </c>
       <c r="R42" t="n">
-        <v>510.436267394789</v>
+        <v>708</v>
       </c>
       <c r="S42" t="n">
-        <v>331.6483886069102</v>
+        <v>708</v>
       </c>
       <c r="T42" t="n">
-        <v>331.6483886069102</v>
+        <v>708</v>
       </c>
       <c r="U42" t="n">
-        <v>330.3435039497136</v>
+        <v>550.5236363636363</v>
       </c>
       <c r="V42" t="n">
-        <v>330.3435039497136</v>
+        <v>371.7357575757576</v>
       </c>
       <c r="W42" t="n">
-        <v>151.5556251618348</v>
+        <v>371.7357575757576</v>
       </c>
       <c r="X42" t="n">
-        <v>151.5556251618348</v>
+        <v>371.7357575757576</v>
       </c>
       <c r="Y42" t="n">
-        <v>151.5556251618348</v>
+        <v>371.7357575757576</v>
       </c>
     </row>
     <row r="43">
@@ -7575,34 +7575,34 @@
         <v>78.8991206524513</v>
       </c>
       <c r="O43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="P43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="R43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="S43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="T43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="U43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="V43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="W43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="X43" t="n">
-        <v>78.8991206524513</v>
+        <v>14.16</v>
       </c>
       <c r="Y43" t="n">
         <v>14.16</v>
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>54.9243204753781</v>
+        <v>14.16</v>
       </c>
       <c r="C44" t="n">
-        <v>54.9243204753781</v>
+        <v>14.16</v>
       </c>
       <c r="D44" t="n">
-        <v>54.9243204753781</v>
+        <v>14.16</v>
       </c>
       <c r="E44" t="n">
-        <v>54.9243204753781</v>
+        <v>14.16</v>
       </c>
       <c r="F44" t="n">
-        <v>54.9243204753781</v>
+        <v>14.16</v>
       </c>
       <c r="G44" t="n">
-        <v>54.9243204753781</v>
+        <v>14.16</v>
       </c>
       <c r="H44" t="n">
-        <v>54.9243204753781</v>
+        <v>14.16</v>
       </c>
       <c r="I44" t="n">
         <v>14.16</v>
@@ -7663,28 +7663,28 @@
         <v>708</v>
       </c>
       <c r="R44" t="n">
-        <v>708</v>
+        <v>601.4813300500959</v>
       </c>
       <c r="S44" t="n">
-        <v>708</v>
+        <v>601.4813300500959</v>
       </c>
       <c r="T44" t="n">
-        <v>529.2121212121212</v>
+        <v>550.5236363636363</v>
       </c>
       <c r="U44" t="n">
-        <v>529.2121212121212</v>
+        <v>371.7357575757576</v>
       </c>
       <c r="V44" t="n">
-        <v>529.2121212121212</v>
+        <v>371.7357575757576</v>
       </c>
       <c r="W44" t="n">
-        <v>350.4242424242424</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="X44" t="n">
-        <v>233.7121992632569</v>
+        <v>14.16</v>
       </c>
       <c r="Y44" t="n">
-        <v>54.9243204753781</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="45">
@@ -7694,46 +7694,46 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>152.5657261719358</v>
+        <v>330.6382875968093</v>
       </c>
       <c r="C45" t="n">
-        <v>152.5657261719358</v>
+        <v>330.6382875968093</v>
       </c>
       <c r="D45" t="n">
-        <v>152.5657261719358</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="E45" t="n">
-        <v>152.5657261719358</v>
+        <v>14.16</v>
       </c>
       <c r="F45" t="n">
-        <v>152.5657261719358</v>
+        <v>14.16</v>
       </c>
       <c r="G45" t="n">
-        <v>152.5657261719358</v>
+        <v>14.16</v>
       </c>
       <c r="H45" t="n">
-        <v>152.5657261719358</v>
+        <v>14.16</v>
       </c>
       <c r="I45" t="n">
         <v>14.16</v>
       </c>
       <c r="J45" t="n">
-        <v>14.16</v>
+        <v>189.39</v>
       </c>
       <c r="K45" t="n">
-        <v>189.39</v>
+        <v>211.5129982060378</v>
       </c>
       <c r="L45" t="n">
-        <v>245.7550534056604</v>
+        <v>320.3480516116982</v>
       </c>
       <c r="M45" t="n">
-        <v>420.9850534056604</v>
+        <v>487.1499066763456</v>
       </c>
       <c r="N45" t="n">
-        <v>596.2150534056603</v>
+        <v>487.1499066763456</v>
       </c>
       <c r="O45" t="n">
-        <v>641.8351467293148</v>
+        <v>532.77</v>
       </c>
       <c r="P45" t="n">
         <v>708</v>
@@ -7757,13 +7757,13 @@
         <v>330.6382875968093</v>
       </c>
       <c r="W45" t="n">
-        <v>152.5657261719358</v>
+        <v>330.6382875968093</v>
       </c>
       <c r="X45" t="n">
-        <v>152.5657261719358</v>
+        <v>330.6382875968093</v>
       </c>
       <c r="Y45" t="n">
-        <v>152.5657261719358</v>
+        <v>330.6382875968093</v>
       </c>
     </row>
     <row r="46">
@@ -7830,19 +7830,19 @@
         <v>77.90912065245131</v>
       </c>
       <c r="U46" t="n">
-        <v>77.90912065245131</v>
+        <v>14.16</v>
       </c>
       <c r="V46" t="n">
-        <v>77.90912065245131</v>
+        <v>14.16</v>
       </c>
       <c r="W46" t="n">
-        <v>77.90912065245131</v>
+        <v>14.16</v>
       </c>
       <c r="X46" t="n">
-        <v>77.90912065245131</v>
+        <v>14.16</v>
       </c>
       <c r="Y46" t="n">
-        <v>77.90912065245131</v>
+        <v>14.16</v>
       </c>
     </row>
   </sheetData>
@@ -8046,22 +8046,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>209.6535371656184</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>175.0656026205451</v>
       </c>
       <c r="M3" t="n">
-        <v>417.2747782656032</v>
+        <v>185.2747782656032</v>
       </c>
       <c r="N3" t="n">
         <v>146.0325997042048</v>
       </c>
       <c r="O3" t="n">
-        <v>143.7154161070223</v>
+        <v>178.1516628920381</v>
       </c>
       <c r="P3" t="n">
-        <v>187.1553865711792</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8283,22 +8283,22 @@
         <v>32.49552059577307</v>
       </c>
       <c r="K6" t="n">
-        <v>209.6535371656184</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>152.7655397861634</v>
       </c>
       <c r="M6" t="n">
         <v>417.2747782656032</v>
       </c>
       <c r="N6" t="n">
-        <v>378.0325997042048</v>
+        <v>146.0325997042048</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>185.9190976528743</v>
       </c>
       <c r="P6" t="n">
-        <v>84.18648684459851</v>
+        <v>187.1553865711792</v>
       </c>
       <c r="Q6" t="n">
         <v>17.27519534353338</v>
@@ -8447,13 +8447,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>299.9100929087363</v>
+        <v>285.9047507578952</v>
       </c>
       <c r="N8" t="n">
         <v>214.7110887231016</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>14.00534215084095</v>
       </c>
       <c r="P8" t="n">
         <v>20.70411531706333</v>
@@ -8520,19 +8520,19 @@
         <v>32.49552059577307</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>209.6535371656184</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>417.2747782656032</v>
+        <v>314.3058785390224</v>
       </c>
       <c r="N9" t="n">
-        <v>298.7981394903682</v>
+        <v>378.0325997042048</v>
       </c>
       <c r="O9" t="n">
-        <v>185.9190976528743</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>187.1553865711792</v>
@@ -8672,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -8751,25 +8751,25 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>175.0656026205451</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>210.0743751450887</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>102.9877604737872</v>
       </c>
       <c r="O12" t="n">
-        <v>185.9190976528743</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -8833,7 +8833,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J13" t="n">
-        <v>134.2003162992274</v>
+        <v>127.8072651351352</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -9000,10 +9000,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>304.1406009832479</v>
+        <v>189.2747782656032</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>132.1410180611778</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -9161,7 +9161,7 @@
         <v>57.90475075789521</v>
       </c>
       <c r="N17" t="n">
-        <v>174.3776771837816</v>
+        <v>201.0724256579518</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9173,7 +9173,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>245.6671196789322</v>
+        <v>224.994599584765</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -9225,7 +9225,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>17.72758189252907</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -9234,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>175.0656026205451</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -9243,13 +9243,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>185.9190976528743</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -9383,10 +9383,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>120.6470157237802</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>6.676213088571487</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9410,7 +9410,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>294.54111633436</v>
+        <v>224.994599584765</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -9462,10 +9462,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>17.72758189252907</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>173.5768572741013</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -9477,7 +9477,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>329.8274362372954</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -9486,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -9544,7 +9544,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J22" t="n">
-        <v>134.2003162992274</v>
+        <v>126.8072651351352</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -9620,10 +9620,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>20.67252009416694</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9705,7 +9705,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>209.6535371656184</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -9714,16 +9714,16 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>25.17796070226461</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>173.9546493319213</v>
       </c>
       <c r="P24" t="n">
-        <v>187.1553865711792</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -9936,10 +9936,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>17.72758189252907</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>157.8654050972496</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -9957,7 +9957,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>113.8776055646682</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>17.27519534353338</v>
@@ -10018,7 +10018,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J28" t="n">
-        <v>134.2003162992274</v>
+        <v>87.80726513513518</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -10094,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2.003692994404545</v>
+        <v>2.00369299440456</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>193.5578254626138</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -10173,13 +10173,13 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>17.22402732447215</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>199.2353130175441</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>154.6535371656184</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -10197,7 +10197,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -10255,7 +10255,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J31" t="n">
-        <v>87.80726513513515</v>
+        <v>134.2003162992274</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>202.208579627842</v>
+        <v>285.9047507578952</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -10410,31 +10410,31 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>17.72758189252907</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>27.87872059577307</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>154.6535371656184</v>
       </c>
       <c r="L33" t="n">
-        <v>120.0656026205451</v>
+        <v>63.27934783921945</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>323.0325997042048</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>130.9190976528743</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -10568,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>120.6470157237802</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -10580,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>285.9047507578952</v>
       </c>
       <c r="N35" t="n">
-        <v>214.7110887231016</v>
+        <v>119.6530747047185</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>13.93270442798791</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10647,7 +10647,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>17.72758189252907</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -10662,16 +10662,16 @@
         <v>362.2747782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>146.0325997042048</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>44.70340564341475</v>
       </c>
       <c r="Q36" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -10729,7 +10729,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J37" t="n">
-        <v>72.99332689903949</v>
+        <v>34.80726513513515</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>120.6470157237802</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>285.9047507578952</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>140.5578254626138</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10832,7 +10832,7 @@
         <v>13.93270442798791</v>
       </c>
       <c r="R38" t="n">
-        <v>238.0253885498012</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -10887,28 +10887,28 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>27.87872059577307</v>
       </c>
       <c r="K39" t="n">
-        <v>57.67470856290674</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>120.0656026205451</v>
       </c>
       <c r="M39" t="n">
         <v>362.2747782656032</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>189.3521852416447</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>130.9190976528743</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -11054,10 +11054,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>282.1992642311093</v>
+        <v>136.8467367395122</v>
       </c>
       <c r="N41" t="n">
-        <v>65.65307470471855</v>
+        <v>160.7110887231016</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11133,10 +11133,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>362.2747782656032</v>
+        <v>294.3377190221316</v>
       </c>
       <c r="N42" t="n">
-        <v>160.6747085629068</v>
+        <v>323.0325997042048</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -11291,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>145.304023171673</v>
+        <v>137.8467367395122</v>
       </c>
       <c r="N44" t="n">
         <v>161.7110887231016</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.93270442798791</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,25 +11361,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>27.87872059577307</v>
+        <v>204.8787205957731</v>
       </c>
       <c r="K45" t="n">
-        <v>101.6535371656184</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>309.2747782656032</v>
+        <v>353.7615005531258</v>
       </c>
       <c r="N45" t="n">
-        <v>323.0325997042048</v>
+        <v>133.189280658635</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>21.98857169308347</v>
+        <v>132.1553865711792</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22512,10 +22512,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -22569,16 +22569,16 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>271.1649506837621</v>
+        <v>189.0855284494863</v>
       </c>
       <c r="V2" t="n">
-        <v>229.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>137.0595741779595</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -22636,7 +22636,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>72.58809527915881</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -22691,13 +22691,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>156.7854556201183</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>211.8407738011431</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -22709,13 +22709,13 @@
         <v>70.18707527168488</v>
       </c>
       <c r="O4" t="n">
-        <v>147.1575640790149</v>
+        <v>135.9912346330881</v>
       </c>
       <c r="P4" t="n">
         <v>207.6238973282775</v>
       </c>
       <c r="Q4" t="n">
-        <v>259.4069369796712</v>
+        <v>270.573266425598</v>
       </c>
       <c r="R4" t="n">
         <v>296.926127981151</v>
@@ -22749,22 +22749,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.7398019077844538</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.286015503096621</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22803,19 +22803,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>180.2347174069558</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>49.55428175152787</v>
+        <v>249.1035880058971</v>
       </c>
       <c r="V5" t="n">
-        <v>229.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>260.4348386588129</v>
+        <v>6.373475980947546</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -22916,13 +22916,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>247.3815003372045</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>244.38387284153</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -22946,19 +22946,19 @@
         <v>70.18707527168488</v>
       </c>
       <c r="O7" t="n">
-        <v>135.9912346330881</v>
+        <v>147.1575640790149</v>
       </c>
       <c r="P7" t="n">
         <v>207.6238973282775</v>
       </c>
       <c r="Q7" t="n">
-        <v>270.573266425598</v>
+        <v>259.4069369796712</v>
       </c>
       <c r="R7" t="n">
         <v>296.926127981151</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>350.8714797028554</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -22989,25 +22989,25 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.286015503096621</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>93.35667727062432</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -23046,10 +23046,10 @@
         <v>249.1035880058971</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>203.8871302094452</v>
       </c>
       <c r="W8" t="n">
-        <v>76.63513570839245</v>
+        <v>6.373475980947546</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -23113,7 +23113,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>98.39553314143586</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>209.5319219073565</v>
       </c>
     </row>
     <row r="10">
@@ -23183,7 +23183,7 @@
         <v>70.18707527168488</v>
       </c>
       <c r="O10" t="n">
-        <v>135.9912346330881</v>
+        <v>147.1575640790149</v>
       </c>
       <c r="P10" t="n">
         <v>207.6238973282775</v>
@@ -23192,7 +23192,7 @@
         <v>270.573266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>696.926127981151</v>
+        <v>296.926127981151</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -23223,25 +23223,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254.9993129555745</v>
+        <v>22.99931295557451</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>222.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>183.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>177.8896287080119</v>
       </c>
       <c r="G11" t="n">
         <v>175.2860155030966</v>
       </c>
       <c r="H11" t="n">
-        <v>75.32302259808534</v>
+        <v>165.9411260402108</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.31962508875506</v>
+        <v>234.3196250887551</v>
       </c>
       <c r="T11" t="n">
         <v>353.2347174069558</v>
@@ -23289,10 +23289,10 @@
         <v>411.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>365.2818334606677</v>
+        <v>289.6386788073863</v>
       </c>
       <c r="Y11" t="n">
-        <v>284.3174326828064</v>
+        <v>52.31743268280638</v>
       </c>
     </row>
     <row r="12">
@@ -23302,22 +23302,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>137.7512177781232</v>
       </c>
       <c r="C12" t="n">
-        <v>134.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>120.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>115.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>112.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>97.95229059200848</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -23356,22 +23356,22 @@
         <v>224.9412641155547</v>
       </c>
       <c r="T12" t="n">
-        <v>26.00602989021397</v>
+        <v>175.1846142741176</v>
       </c>
       <c r="U12" t="n">
-        <v>173.1585673073565</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>187.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>205.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>192.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>172.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -23393,7 +23393,7 @@
         <v>53.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>32.62733200497873</v>
+        <v>47.38285596774193</v>
       </c>
       <c r="G13" t="n">
         <v>17.38387284153003</v>
@@ -23414,22 +23414,22 @@
         <v>98.42362815777916</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>190.1736114025499</v>
       </c>
       <c r="N13" t="n">
-        <v>11.18707527168486</v>
+        <v>243.1870752716849</v>
       </c>
       <c r="O13" t="n">
         <v>320.1575640790149</v>
       </c>
       <c r="P13" t="n">
-        <v>380.6238973282775</v>
+        <v>148.6238973282775</v>
       </c>
       <c r="Q13" t="n">
         <v>443.573266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>469.9261279811511</v>
+        <v>264.9969926158379</v>
       </c>
       <c r="S13" t="n">
         <v>123.8714797028554</v>
@@ -23463,7 +23463,7 @@
         <v>253.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>221.4745782429939</v>
+        <v>132.4092600230546</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -23472,10 +23472,10 @@
         <v>176.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>176.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>174.2860155030966</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23511,13 +23511,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>233.3196250887551</v>
+        <v>1.31962508875506</v>
       </c>
       <c r="T14" t="n">
         <v>352.2347174069558</v>
       </c>
       <c r="U14" t="n">
-        <v>219.2139139970662</v>
+        <v>421.1035880058971</v>
       </c>
       <c r="V14" t="n">
         <v>401.8510241668239</v>
@@ -23526,7 +23526,7 @@
         <v>410.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>364.2818334606677</v>
+        <v>132.2818334606677</v>
       </c>
       <c r="Y14" t="n">
         <v>283.3174326828064</v>
@@ -23539,22 +23539,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.78052993381283</v>
+        <v>156.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>133.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>119.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>114.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>111.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>96.95229059200848</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>96.56495511094943</v>
@@ -23590,13 +23590,13 @@
         <v>270.3955331414359</v>
       </c>
       <c r="S15" t="n">
-        <v>223.9412641155547</v>
+        <v>4.758354225007309</v>
       </c>
       <c r="T15" t="n">
         <v>174.1846142741176</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>172.1585673073565</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -23605,10 +23605,10 @@
         <v>204.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>191.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>171.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -23633,7 +23633,7 @@
         <v>46.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>16.38387284153003</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23648,19 +23648,19 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>97.42362815777916</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>189.1736114025499</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>66.22475817800938</v>
+        <v>144.4598323161633</v>
       </c>
       <c r="O16" t="n">
         <v>319.1575640790149</v>
       </c>
       <c r="P16" t="n">
-        <v>147.6238973282775</v>
+        <v>379.6238973282775</v>
       </c>
       <c r="Q16" t="n">
         <v>442.573266425598</v>
@@ -23684,10 +23684,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>19.44364543010755</v>
       </c>
       <c r="Y16" t="n">
-        <v>59.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -23703,7 +23703,7 @@
         <v>221.4745782429939</v>
       </c>
       <c r="D17" t="n">
-        <v>182.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>176.3632896068686</v>
@@ -23712,7 +23712,7 @@
         <v>176.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>174.2860155030966</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>164.9411260402108</v>
@@ -23748,25 +23748,25 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.31962508875506</v>
+        <v>233.3196250887551</v>
       </c>
       <c r="T17" t="n">
-        <v>352.2347174069558</v>
+        <v>120.2347174069558</v>
       </c>
       <c r="U17" t="n">
-        <v>421.1035880058971</v>
+        <v>341.3831592488437</v>
       </c>
       <c r="V17" t="n">
-        <v>169.8510241668239</v>
+        <v>401.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>206.0278759809476</v>
+        <v>410.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>364.2818334606677</v>
+        <v>132.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>51.31743268280638</v>
+        <v>283.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -23779,7 +23779,7 @@
         <v>156.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>133.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>119.9376868977026</v>
@@ -23788,13 +23788,13 @@
         <v>114.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>111.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>96.95229059200848</v>
+        <v>96.95229059200847</v>
       </c>
       <c r="H18" t="n">
-        <v>92.32733609546577</v>
+        <v>96.56495511094943</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23827,7 +23827,7 @@
         <v>270.3955331414359</v>
       </c>
       <c r="S18" t="n">
-        <v>223.9412641155547</v>
+        <v>106.5377399258125</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -23836,7 +23836,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>186.5106671915202</v>
       </c>
       <c r="W18" t="n">
         <v>204.3731429098285</v>
@@ -23845,7 +23845,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>171.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -23855,22 +23855,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>59.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>44.72524664804467</v>
+        <v>20.87934214775916</v>
       </c>
       <c r="D19" t="n">
         <v>57.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>52.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>46.38285596774193</v>
       </c>
       <c r="G19" t="n">
-        <v>16.38387284153003</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -23885,16 +23885,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>97.42362815777916</v>
+        <v>97.42362815777915</v>
       </c>
       <c r="M19" t="n">
         <v>189.1736114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>10.18707527168486</v>
+        <v>242.1870752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>230.2392084165573</v>
+        <v>87.15756407901495</v>
       </c>
       <c r="P19" t="n">
         <v>379.6238973282775</v>
@@ -23903,10 +23903,10 @@
         <v>442.573266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>468.9261279811511</v>
+        <v>468.926127981151</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>122.8714797028554</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>19.44364543010755</v>
       </c>
       <c r="Y19" t="n">
-        <v>59.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -23934,7 +23934,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253.9993129555745</v>
+        <v>21.99931295557451</v>
       </c>
       <c r="C20" t="n">
         <v>221.4745782429939</v>
@@ -23949,10 +23949,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>174.2860155030966</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>164.9411260402108</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23985,22 +23985,22 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.31962508875506</v>
+        <v>233.3196250887551</v>
       </c>
       <c r="T20" t="n">
-        <v>352.2347174069558</v>
+        <v>120.2347174069559</v>
       </c>
       <c r="U20" t="n">
         <v>421.1035880058971</v>
       </c>
       <c r="V20" t="n">
-        <v>169.8510241668239</v>
+        <v>316.6810683779324</v>
       </c>
       <c r="W20" t="n">
         <v>410.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>269.7669882088905</v>
+        <v>364.2818334606677</v>
       </c>
       <c r="Y20" t="n">
         <v>283.3174326828064</v>
@@ -24013,7 +24013,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>156.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>133.0999124455193</v>
@@ -24025,10 +24025,10 @@
         <v>114.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>111.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>96.95229059200848</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -24070,19 +24070,19 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>172.1585673073565</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>45.08258913164926</v>
+        <v>204.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>191.8627394453875</v>
+        <v>173.6776160264444</v>
       </c>
       <c r="Y21" t="n">
-        <v>171.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -24092,22 +24092,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>44.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>22.07900912759142</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>52.98090483695654</v>
       </c>
       <c r="F22" t="n">
-        <v>46.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>16.38387284153003</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -24122,13 +24122,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>97.42362815777916</v>
       </c>
       <c r="M22" t="n">
         <v>189.1736114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>242.1870752716849</v>
+        <v>41.98287918643013</v>
       </c>
       <c r="O22" t="n">
         <v>319.1575640790149</v>
@@ -24140,7 +24140,7 @@
         <v>442.573266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>236.9261279811511</v>
+        <v>468.9261279811511</v>
       </c>
       <c r="S22" t="n">
         <v>122.8714797028554</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>59.46535284946236</v>
       </c>
     </row>
     <row r="23">
@@ -24174,10 +24174,10 @@
         <v>253.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>221.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>182.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>176.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>79.24483115017615</v>
+        <v>174.2860155030966</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,10 +24222,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31962508875506</v>
+        <v>233.3196250887551</v>
       </c>
       <c r="T23" t="n">
-        <v>352.2347174069558</v>
+        <v>197.0072670368791</v>
       </c>
       <c r="U23" t="n">
         <v>421.1035880058971</v>
@@ -24237,7 +24237,7 @@
         <v>410.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>132.2818334606677</v>
+        <v>364.2818334606677</v>
       </c>
       <c r="Y23" t="n">
         <v>283.3174326828064</v>
@@ -24250,25 +24250,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>156.5565566463266</v>
+        <v>150.3127208277501</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>119.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>114.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>111.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>96.95229059200848</v>
       </c>
       <c r="H24" t="n">
-        <v>96.56495511094943</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24298,16 +24298,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>267.577623595529</v>
+        <v>270.3955331414359</v>
       </c>
       <c r="S24" t="n">
         <v>223.9412641155547</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>174.1846142741176</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>172.1585673073565</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -24316,10 +24316,10 @@
         <v>204.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>191.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>171.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24329,7 +24329,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>59.11380033707866</v>
+        <v>10.70839184452526</v>
       </c>
       <c r="C25" t="n">
         <v>44.72524664804467</v>
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>52.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -24371,13 +24371,13 @@
         <v>319.1575640790149</v>
       </c>
       <c r="P25" t="n">
-        <v>147.6238973282775</v>
+        <v>379.6238973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>387.6834099205388</v>
+        <v>442.573266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>468.9261279811511</v>
+        <v>236.9261279811511</v>
       </c>
       <c r="S25" t="n">
         <v>122.8714797028554</v>
@@ -24398,7 +24398,7 @@
         <v>19.44364543010755</v>
       </c>
       <c r="Y25" t="n">
-        <v>59.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -24411,10 +24411,10 @@
         <v>269.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>237.4745782429939</v>
+        <v>60.47457824299249</v>
       </c>
       <c r="D26" t="n">
-        <v>198.3391557398498</v>
+        <v>21.33915573984837</v>
       </c>
       <c r="E26" t="n">
         <v>192.3632896068686</v>
@@ -24426,7 +24426,7 @@
         <v>190.2860155030966</v>
       </c>
       <c r="H26" t="n">
-        <v>180.9411260402108</v>
+        <v>3.941126040207905</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,10 +24459,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>72.31962508875267</v>
+        <v>249.3196250887551</v>
       </c>
       <c r="T26" t="n">
-        <v>212.3331174069609</v>
+        <v>368.2347174069558</v>
       </c>
       <c r="U26" t="n">
         <v>437.1035880058971</v>
@@ -24471,13 +24471,13 @@
         <v>417.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>249.3734759809463</v>
+        <v>270.4718759809534</v>
       </c>
       <c r="X26" t="n">
         <v>380.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>122.317432682805</v>
+        <v>299.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24490,22 +24490,22 @@
         <v>172.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>81.96158460596938</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>135.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>127.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>112.9522905920085</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>112.5649551109494</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24541,7 +24541,7 @@
         <v>239.9412641155547</v>
       </c>
       <c r="T27" t="n">
-        <v>190.1846142741176</v>
+        <v>137.055023941552</v>
       </c>
       <c r="U27" t="n">
         <v>188.1585673073565</v>
@@ -24553,10 +24553,10 @@
         <v>220.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>207.8627394453875</v>
+        <v>30.8627394453863</v>
       </c>
       <c r="Y27" t="n">
-        <v>187.3913927661343</v>
+        <v>10.39139276613309</v>
       </c>
     </row>
     <row r="28">
@@ -24569,7 +24569,7 @@
         <v>75.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>60.72524664804467</v>
       </c>
       <c r="D28" t="n">
         <v>73.53621805555548</v>
@@ -24578,13 +24578,13 @@
         <v>68.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>62.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>32.38387284153004</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>10.90312610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24605,13 +24605,13 @@
         <v>258.1870752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>335.1575640790149</v>
+        <v>158.1575640790149</v>
       </c>
       <c r="P28" t="n">
         <v>395.6238973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>409.9204504922765</v>
+        <v>330.6871862451691</v>
       </c>
       <c r="R28" t="n">
         <v>484.9261279811511</v>
@@ -24629,13 +24629,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>14.37280983870968</v>
       </c>
       <c r="X28" t="n">
         <v>35.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>75.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -24645,7 +24645,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>269.9993129555745</v>
+        <v>114.0977129555745</v>
       </c>
       <c r="C29" t="n">
         <v>237.4745782429939</v>
@@ -24660,10 +24660,10 @@
         <v>192.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>13.28601550309661</v>
+        <v>13.28601550309662</v>
       </c>
       <c r="H29" t="n">
-        <v>25.03952604021083</v>
+        <v>180.9411260402108</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,22 +24696,22 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>72.31962508875506</v>
+        <v>249.3196250887551</v>
       </c>
       <c r="T29" t="n">
         <v>368.2347174069558</v>
       </c>
       <c r="U29" t="n">
-        <v>437.1035880058971</v>
+        <v>260.1035880058971</v>
       </c>
       <c r="V29" t="n">
-        <v>417.8510241668239</v>
+        <v>240.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>426.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>203.2818334606677</v>
+        <v>380.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>299.3174326828064</v>
@@ -24730,7 +24730,7 @@
         <v>149.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>135.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -24739,10 +24739,10 @@
         <v>127.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>46.66047471162375</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>112.5649551109494</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -24781,10 +24781,10 @@
         <v>190.1846142741176</v>
       </c>
       <c r="U30" t="n">
-        <v>34.44631023222715</v>
+        <v>11.15856730735655</v>
       </c>
       <c r="V30" t="n">
-        <v>25.51066719152016</v>
+        <v>202.5106671915202</v>
       </c>
       <c r="W30" t="n">
         <v>220.3731429098285</v>
@@ -24793,7 +24793,7 @@
         <v>207.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>187.3913927661343</v>
+        <v>10.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -24803,25 +24803,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>75.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>60.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>73.53621805555548</v>
       </c>
       <c r="E31" t="n">
         <v>68.98090483695654</v>
       </c>
       <c r="F31" t="n">
-        <v>62.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>32.38387284153004</v>
+        <v>27.60589527688782</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>10.90312610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>113.4236281577791</v>
       </c>
       <c r="M31" t="n">
         <v>205.1736114025499</v>
@@ -24848,10 +24848,10 @@
         <v>395.6238973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>458.573266425598</v>
+        <v>281.573266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>484.9261279811511</v>
+        <v>484.926127981151</v>
       </c>
       <c r="S31" t="n">
         <v>138.8714797028554</v>
@@ -24872,7 +24872,7 @@
         <v>35.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>43.55604532106545</v>
+        <v>75.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -24882,10 +24882,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>39.99931295557451</v>
+        <v>160.7470180655398</v>
       </c>
       <c r="C32" t="n">
-        <v>184.4745782429939</v>
+        <v>7.474578242993914</v>
       </c>
       <c r="D32" t="n">
         <v>145.3391557398498</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>71.68883115017609</v>
+        <v>127.9411260402108</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>19.31962508875506</v>
+        <v>196.3196250887551</v>
       </c>
       <c r="T32" t="n">
         <v>315.2347174069558</v>
@@ -24942,7 +24942,7 @@
         <v>384.1035880058971</v>
       </c>
       <c r="V32" t="n">
-        <v>364.8510241668239</v>
+        <v>187.8510241668239</v>
       </c>
       <c r="W32" t="n">
         <v>373.3734759809475</v>
@@ -24964,7 +24964,7 @@
         <v>119.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>96.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>82.93768689770263</v>
@@ -24976,10 +24976,10 @@
         <v>74.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>59.95229059200847</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>59.56495511094943</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -25009,19 +25009,19 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>69.79976661381684</v>
+        <v>233.3955331414359</v>
       </c>
       <c r="S33" t="n">
         <v>186.9412641155547</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>137.1846142741176</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>6.53901241335663</v>
       </c>
       <c r="V33" t="n">
-        <v>149.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>167.3731429098285</v>
@@ -25030,7 +25030,7 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>134.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25070,22 +25070,22 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>60.42362815777915</v>
       </c>
       <c r="M34" t="n">
-        <v>152.1736114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>28.18707527168488</v>
+        <v>205.1870752716849</v>
       </c>
       <c r="O34" t="n">
         <v>105.1575640790149</v>
       </c>
       <c r="P34" t="n">
-        <v>174.1088194736153</v>
+        <v>165.6238973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>405.573266425598</v>
+        <v>328.8081718157065</v>
       </c>
       <c r="R34" t="n">
         <v>431.926127981151</v>
@@ -25125,19 +25125,19 @@
         <v>184.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>145.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>139.3632896068686</v>
       </c>
       <c r="F35" t="n">
-        <v>139.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>127.9411260402108</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25170,19 +25170,19 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>128.6451666320626</v>
+        <v>19.31962508875506</v>
       </c>
       <c r="T35" t="n">
         <v>315.2347174069558</v>
       </c>
       <c r="U35" t="n">
-        <v>207.1035880058971</v>
+        <v>384.1035880058971</v>
       </c>
       <c r="V35" t="n">
-        <v>364.8510241668239</v>
+        <v>277.4642241177821</v>
       </c>
       <c r="W35" t="n">
-        <v>196.3734759809475</v>
+        <v>373.3734759809475</v>
       </c>
       <c r="X35" t="n">
         <v>327.2818334606677</v>
@@ -25201,10 +25201,10 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>96.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>82.93768689770263</v>
       </c>
       <c r="E36" t="n">
         <v>77.67209722191262</v>
@@ -25216,7 +25216,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>59.56495511094943</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -25252,22 +25252,22 @@
         <v>186.9412641155547</v>
       </c>
       <c r="T36" t="n">
-        <v>137.1846142741176</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>135.1585673073566</v>
+        <v>128.8408033692081</v>
       </c>
       <c r="V36" t="n">
         <v>149.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>128.0819263855993</v>
+        <v>167.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>134.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -25289,7 +25289,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>9.382855967741932</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -25307,16 +25307,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>60.42362815777916</v>
       </c>
       <c r="M37" t="n">
         <v>152.1736114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>205.1870752716849</v>
+        <v>28.18707527168486</v>
       </c>
       <c r="O37" t="n">
-        <v>282.1575640790149</v>
+        <v>230.2188580665735</v>
       </c>
       <c r="P37" t="n">
         <v>165.6238973282775</v>
@@ -25325,10 +25325,10 @@
         <v>228.573266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>339.8996738616023</v>
+        <v>431.9261279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>85.87147970285544</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25365,7 +25365,7 @@
         <v>145.3391557398498</v>
       </c>
       <c r="E38" t="n">
-        <v>139.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>139.8896287080119</v>
@@ -25374,7 +25374,7 @@
         <v>137.2860155030966</v>
       </c>
       <c r="H38" t="n">
-        <v>127.9411260402108</v>
+        <v>111.4028156470795</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>196.3196250887551</v>
+        <v>19.31962508875506</v>
       </c>
       <c r="T38" t="n">
         <v>315.2347174069558</v>
@@ -25419,10 +25419,10 @@
         <v>187.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>217.4718759809475</v>
+        <v>373.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>150.2818334606677</v>
+        <v>327.2818334606677</v>
       </c>
       <c r="Y38" t="n">
         <v>246.3174326828064</v>
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>119.5565566463266</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>59.95229059200847</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>59.56495511094943</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -25483,28 +25483,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>176.4261914459367</v>
+        <v>233.3955331414359</v>
       </c>
       <c r="S39" t="n">
         <v>186.9412641155547</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>137.1846142741176</v>
       </c>
       <c r="U39" t="n">
-        <v>135.1585673073566</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>149.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>167.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>154.8627394453875</v>
+        <v>140.6956083914974</v>
       </c>
       <c r="Y39" t="n">
-        <v>134.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25544,7 +25544,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>60.42362815777915</v>
       </c>
       <c r="M40" t="n">
         <v>152.1736114025499</v>
@@ -25553,16 +25553,16 @@
         <v>205.1870752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>105.1575640790149</v>
+        <v>139.090337769429</v>
       </c>
       <c r="P40" t="n">
         <v>165.6238973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>322.9296682737913</v>
+        <v>405.573266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>431.926127981151</v>
+        <v>254.926127981151</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>427.9993129555745</v>
+        <v>250.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>395.4745782429939</v>
@@ -25602,16 +25602,16 @@
         <v>356.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>173.3632896068686</v>
+        <v>350.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>350.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>171.2860155030966</v>
+        <v>348.2860155030966</v>
       </c>
       <c r="H41" t="n">
-        <v>338.9411260402108</v>
+        <v>222.3962033108351</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,7 +25641,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>104.453483250405</v>
       </c>
       <c r="S41" t="n">
         <v>230.3196250887551</v>
@@ -25650,10 +25650,10 @@
         <v>526.2347174069558</v>
       </c>
       <c r="U41" t="n">
-        <v>583.0121485269265</v>
+        <v>595.1035880058971</v>
       </c>
       <c r="V41" t="n">
-        <v>575.8510241668239</v>
+        <v>398.8510241668239</v>
       </c>
       <c r="W41" t="n">
         <v>584.3734759809475</v>
@@ -25672,7 +25672,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>330.5565566463266</v>
+        <v>153.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>307.0999124455193</v>
@@ -25690,10 +25690,10 @@
         <v>270.9522905920085</v>
       </c>
       <c r="H42" t="n">
-        <v>270.5649551109494</v>
+        <v>93.56495511094943</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>136.0216689102165</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25717,25 +25717,25 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>18.58809527915881</v>
       </c>
       <c r="R42" t="n">
-        <v>267.3955331414359</v>
+        <v>444.3955331414359</v>
       </c>
       <c r="S42" t="n">
-        <v>220.9412641155547</v>
+        <v>397.9412641155547</v>
       </c>
       <c r="T42" t="n">
         <v>348.1846142741176</v>
       </c>
       <c r="U42" t="n">
-        <v>344.866731496732</v>
+        <v>190.2569673073565</v>
       </c>
       <c r="V42" t="n">
-        <v>360.5106671915202</v>
+        <v>183.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>201.3731429098285</v>
+        <v>378.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>365.8627394453875</v>
@@ -25790,7 +25790,7 @@
         <v>416.1870752716849</v>
       </c>
       <c r="O43" t="n">
-        <v>493.1575640790149</v>
+        <v>429.0658346330882</v>
       </c>
       <c r="P43" t="n">
         <v>553.6238973282775</v>
@@ -25820,7 +25820,7 @@
         <v>193.4436454301076</v>
       </c>
       <c r="Y43" t="n">
-        <v>169.3736234035356</v>
+        <v>233.4653528494624</v>
       </c>
     </row>
     <row r="44">
@@ -25851,7 +25851,7 @@
         <v>339.9411260402108</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>40.35667727062432</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25878,16 +25878,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>105.453483250405</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>408.3196250887551</v>
       </c>
       <c r="T44" t="n">
-        <v>350.2347174069558</v>
+        <v>476.7866006573609</v>
       </c>
       <c r="U44" t="n">
-        <v>596.1035880058971</v>
+        <v>419.1035880058971</v>
       </c>
       <c r="V44" t="n">
         <v>576.8510241668239</v>
@@ -25896,10 +25896,10 @@
         <v>408.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>423.736910731292</v>
+        <v>362.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>281.3174326828064</v>
+        <v>458.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25915,10 +25915,10 @@
         <v>308.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>294.9376868977026</v>
+        <v>158.6241821768615</v>
       </c>
       <c r="E45" t="n">
-        <v>289.6720972219126</v>
+        <v>112.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>286.6362423378769</v>
@@ -25930,7 +25930,7 @@
         <v>271.5649551109494</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>137.0216689102165</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>361.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>203.0813070992038</v>
+        <v>379.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>366.8627394453875</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>171.0021708911519</v>
+        <v>234.1138003370787</v>
       </c>
       <c r="C46" t="n">
         <v>219.7252466480447</v>
@@ -26045,7 +26045,7 @@
         <v>154.2045665062577</v>
       </c>
       <c r="U46" t="n">
-        <v>97.92239127445794</v>
+        <v>34.81076182853114</v>
       </c>
       <c r="V46" t="n">
         <v>146.1703102162162</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3150808.395694222</v>
+        <v>3150808.395694221</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3787734.369898241</v>
+        <v>3787734.369898239</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4425039.544134153</v>
+        <v>4425039.54413415</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5062344.718370057</v>
+        <v>5062344.718370059</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5699649.892605962</v>
+        <v>5699649.892605966</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6280945.750494039</v>
+        <v>6280945.750494042</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6873359.30831904</v>
+        <v>6873359.308319043</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7586756.517850855</v>
+        <v>7586756.517850856</v>
       </c>
     </row>
     <row r="13">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8942165.024914488</v>
+        <v>8942165.024914486</v>
       </c>
     </row>
     <row r="15">
@@ -26269,34 +26269,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1232865.374766376</v>
+        <v>1232865.374766375</v>
       </c>
       <c r="C2" t="n">
         <v>1232865.374766375</v>
       </c>
       <c r="D2" t="n">
-        <v>1232865.374766375</v>
+        <v>1232865.374766376</v>
       </c>
       <c r="E2" t="n">
-        <v>953543.7517138665</v>
+        <v>953543.7517138666</v>
       </c>
       <c r="F2" t="n">
+        <v>955957.7613538655</v>
+      </c>
+      <c r="G2" t="n">
         <v>955957.761353866</v>
-      </c>
-      <c r="G2" t="n">
-        <v>955957.7613538664</v>
       </c>
       <c r="H2" t="n">
         <v>955957.7613538658</v>
       </c>
       <c r="I2" t="n">
-        <v>955957.7613538661</v>
+        <v>955957.7613538655</v>
       </c>
       <c r="J2" t="n">
-        <v>888620.3367375106</v>
+        <v>888620.3367375109</v>
       </c>
       <c r="K2" t="n">
-        <v>888620.336737511</v>
+        <v>888620.3367375107</v>
       </c>
       <c r="L2" t="n">
         <v>1016556.380297729</v>
@@ -26308,7 +26308,7 @@
         <v>1016556.380297729</v>
       </c>
       <c r="O2" t="n">
-        <v>485060.0070460041</v>
+        <v>485060.0070460042</v>
       </c>
       <c r="P2" t="n">
         <v>482361.5885260042</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>599568.6781036436</v>
+        <v>599451.1428189974</v>
       </c>
       <c r="C4" t="n">
-        <v>597673.1154498833</v>
+        <v>597555.5801652372</v>
       </c>
       <c r="D4" t="n">
-        <v>595774.9813470705</v>
+        <v>595657.4460624245</v>
       </c>
       <c r="E4" t="n">
-        <v>409716.4475828001</v>
+        <v>409670.6333782462</v>
       </c>
       <c r="F4" t="n">
-        <v>409386.7088868252</v>
+        <v>409341.2464868575</v>
       </c>
       <c r="G4" t="n">
-        <v>407910.2936608223</v>
+        <v>407864.8312608547</v>
       </c>
       <c r="H4" t="n">
-        <v>406431.829254736</v>
+        <v>406386.3668547682</v>
       </c>
       <c r="I4" t="n">
-        <v>404951.3008883421</v>
+        <v>404905.8384883744</v>
       </c>
       <c r="J4" t="n">
-        <v>367261.6318826846</v>
+        <v>367226.4839803365</v>
       </c>
       <c r="K4" t="n">
-        <v>365881.952318557</v>
+        <v>365846.8044162089</v>
       </c>
       <c r="L4" t="n">
-        <v>447150.4923865803</v>
+        <v>447082.2301789545</v>
       </c>
       <c r="M4" t="n">
-        <v>445567.8481651251</v>
+        <v>445499.5859574992</v>
       </c>
       <c r="N4" t="n">
-        <v>443982.9283644496</v>
+        <v>443914.666156824</v>
       </c>
       <c r="O4" t="n">
-        <v>176671.8384048985</v>
+        <v>176584.2414872895</v>
       </c>
       <c r="P4" t="n">
-        <v>175029.3653136219</v>
+        <v>174941.5578142664</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>139070.6966627321</v>
+        <v>139188.231947378</v>
       </c>
       <c r="C6" t="n">
-        <v>579480.2593164917</v>
+        <v>579597.7946011375</v>
       </c>
       <c r="D6" t="n">
-        <v>581378.3934193049</v>
+        <v>581495.9287039512</v>
       </c>
       <c r="E6" t="n">
-        <v>321059.2411310665</v>
+        <v>321105.0553356204</v>
       </c>
       <c r="F6" t="n">
-        <v>504518.9204670407</v>
+        <v>504564.382867008</v>
       </c>
       <c r="G6" t="n">
-        <v>506795.3356930441</v>
+        <v>506840.7980930114</v>
       </c>
       <c r="H6" t="n">
-        <v>508273.8000991299</v>
+        <v>508319.2624990976</v>
       </c>
       <c r="I6" t="n">
-        <v>509754.328465524</v>
+        <v>509799.7908654911</v>
       </c>
       <c r="J6" t="n">
-        <v>253691.676854826</v>
+        <v>253726.8247571744</v>
       </c>
       <c r="K6" t="n">
-        <v>485375.356418954</v>
+        <v>485410.5043213019</v>
       </c>
       <c r="L6" t="n">
-        <v>485987.202911149</v>
+        <v>486055.4651187746</v>
       </c>
       <c r="M6" t="n">
-        <v>529969.8471326041</v>
+        <v>530038.1093402298</v>
       </c>
       <c r="N6" t="n">
-        <v>531554.7669332796</v>
+        <v>531623.029140905</v>
       </c>
       <c r="O6" t="n">
-        <v>285108.0426411057</v>
+        <v>285195.6395587146</v>
       </c>
       <c r="P6" t="n">
-        <v>284136.1662123824</v>
+        <v>284223.9737117378</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -27097,7 +27097,7 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>177</v>
@@ -27442,7 +27442,7 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>400</v>
+        <v>295.7472396581474</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
@@ -27490,7 +27490,7 @@
         <v>400</v>
       </c>
       <c r="U2" t="n">
-        <v>145.938637322135</v>
+        <v>400</v>
       </c>
       <c r="V2" t="n">
         <v>400</v>
@@ -27560,28 +27560,28 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>266.3955331414359</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>219.9412641155547</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>250.2334639366903</v>
       </c>
       <c r="V3" t="n">
         <v>182.5106671915202</v>
       </c>
       <c r="W3" t="n">
-        <v>241.1583564728396</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>167.3913927661343</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27612,13 +27612,13 @@
         <v>222.9031261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>156.7854556201183</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>211.8407738011431</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>325.4236281577791</v>
@@ -27733,7 +27733,7 @@
         <v>400</v>
       </c>
       <c r="W5" t="n">
-        <v>145.9386373221347</v>
+        <v>400</v>
       </c>
       <c r="X5" t="n">
         <v>400</v>
@@ -27755,16 +27755,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>115.9376868977026</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>198.3411208862724</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>92.95229059200848</v>
+        <v>324.9522905920085</v>
       </c>
       <c r="H6" t="n">
         <v>324.5649551109494</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>72.58809527915881</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27803,10 +27803,10 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>170.1846142741176</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>168.1585673073565</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>180.1291395698611</v>
       </c>
     </row>
     <row r="7">
@@ -27837,13 +27837,13 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>33.59940449975208</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>244.38387284153</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>222.9031261016186</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>350.8714797028554</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>207.2045665062577</v>
@@ -27928,7 +27928,7 @@
         <v>392.9411260402108</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>93.35667727062432</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>158.453483250405</v>
       </c>
       <c r="S8" t="n">
-        <v>359.8983296681355</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>152.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>129.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>128.8340010087859</v>
+        <v>264.6230821414678</v>
       </c>
       <c r="E9" t="n">
         <v>110.6720972219126</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>170.1846142741176</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>189.8594708587778</v>
       </c>
     </row>
     <row r="10">
@@ -28113,7 +28113,7 @@
         <v>400</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S10" t="n">
         <v>350.8714797028554</v>
@@ -28122,7 +28122,7 @@
         <v>207.2045665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9223912744579</v>
+        <v>139.7560618285311</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28134,7 +28134,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>227</v>
       </c>
       <c r="I11" t="n">
-        <v>227</v>
+        <v>114.0291973647913</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28180,7 +28180,7 @@
         <v>227</v>
       </c>
       <c r="N11" t="n">
-        <v>222.3873018116731</v>
+        <v>214.7110887231016</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -28244,28 +28244,28 @@
         <v>227</v>
       </c>
       <c r="I12" t="n">
-        <v>227</v>
+        <v>190.0216689102165</v>
       </c>
       <c r="J12" t="n">
-        <v>27.87872059577307</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>209.6535371656184</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>185.2747782656032</v>
       </c>
       <c r="N12" t="n">
         <v>227</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>18.08845799195578</v>
       </c>
       <c r="P12" t="n">
-        <v>125.2807306132175</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>227</v>
@@ -28326,7 +28326,7 @@
         <v>227</v>
       </c>
       <c r="J13" t="n">
-        <v>220.6069488359078</v>
+        <v>227</v>
       </c>
       <c r="K13" t="n">
         <v>227</v>
@@ -28402,10 +28402,10 @@
         <v>228</v>
       </c>
       <c r="I14" t="n">
-        <v>114.0291973647913</v>
+        <v>93.35667727062432</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>20.67252009416694</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -28481,31 +28481,31 @@
         <v>228</v>
       </c>
       <c r="I15" t="n">
+        <v>190.0216689102165</v>
+      </c>
+      <c r="J15" t="n">
+        <v>27.87872059577307</v>
+      </c>
+      <c r="K15" t="n">
+        <v>209.6535371656184</v>
+      </c>
+      <c r="L15" t="n">
+        <v>175.0656026205451</v>
+      </c>
+      <c r="M15" t="n">
         <v>228</v>
       </c>
-      <c r="J15" t="n">
-        <v>228</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
-        <v>228</v>
+        <v>13.89158164302708</v>
       </c>
       <c r="O15" t="n">
-        <v>154.0751484081884</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>228</v>
+        <v>221.5640374730083</v>
       </c>
       <c r="R15" t="n">
         <v>228</v>
@@ -28654,7 +28654,7 @@
         <v>228</v>
       </c>
       <c r="N17" t="n">
-        <v>40.33341153931997</v>
+        <v>34.31118315931685</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -28721,7 +28721,7 @@
         <v>228</v>
       </c>
       <c r="J18" t="n">
-        <v>228</v>
+        <v>27.87872059577307</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -28736,13 +28736,13 @@
         <v>228</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>85.84362149646779</v>
       </c>
       <c r="P18" t="n">
         <v>187.1553865711792</v>
       </c>
       <c r="Q18" t="n">
-        <v>102.4164605109159</v>
+        <v>228</v>
       </c>
       <c r="R18" t="n">
         <v>228</v>
@@ -28876,7 +28876,7 @@
         <v>228</v>
       </c>
       <c r="I20" t="n">
-        <v>93.35667727062432</v>
+        <v>228</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>13.93270442798791</v>
       </c>
       <c r="R20" t="n">
-        <v>179.1260033445722</v>
+        <v>228</v>
       </c>
       <c r="S20" t="n">
         <v>228</v>
@@ -28955,10 +28955,10 @@
         <v>228</v>
       </c>
       <c r="I21" t="n">
-        <v>228</v>
+        <v>207.7492508027455</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>32.41397866798465</v>
       </c>
       <c r="K21" t="n">
         <v>209.6535371656184</v>
@@ -28970,16 +28970,16 @@
         <v>228</v>
       </c>
       <c r="N21" t="n">
-        <v>146.0325997042048</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>156.9527552475114</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>228</v>
+        <v>170.1095818260659</v>
       </c>
       <c r="R21" t="n">
         <v>228</v>
@@ -29037,7 +29037,7 @@
         <v>228</v>
       </c>
       <c r="J22" t="n">
-        <v>220.6069488359078</v>
+        <v>228</v>
       </c>
       <c r="K22" t="n">
         <v>228</v>
@@ -29113,7 +29113,7 @@
         <v>228</v>
       </c>
       <c r="I23" t="n">
-        <v>214.0036929944046</v>
+        <v>93.35667727062432</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29137,7 +29137,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>34.6052245221551</v>
+        <v>13.93270442798791</v>
       </c>
       <c r="R23" t="n">
         <v>158.453483250405</v>
@@ -29201,22 +29201,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>175.0656026205451</v>
       </c>
       <c r="M24" t="n">
         <v>185.2747782656032</v>
       </c>
       <c r="N24" t="n">
-        <v>120.8546390019402</v>
+        <v>146.0325997042048</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>40.89089670522402</v>
       </c>
       <c r="Q24" t="n">
-        <v>203.8270295773594</v>
+        <v>228</v>
       </c>
       <c r="R24" t="n">
         <v>228</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
+        <v>193.5578254626138</v>
+      </c>
+      <c r="N26" t="n">
         <v>212</v>
-      </c>
-      <c r="N26" t="n">
-        <v>193.5578254626138</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -29429,16 +29429,16 @@
         <v>212</v>
       </c>
       <c r="I27" t="n">
-        <v>212</v>
+        <v>207.7492508027455</v>
       </c>
       <c r="J27" t="n">
-        <v>27.87872059577307</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>154.6535371656184</v>
       </c>
       <c r="L27" t="n">
-        <v>109.2135373857574</v>
+        <v>115.0827895387325</v>
       </c>
       <c r="M27" t="n">
         <v>185.2747782656032</v>
@@ -29511,7 +29511,7 @@
         <v>212</v>
       </c>
       <c r="J28" t="n">
-        <v>165.6069488359078</v>
+        <v>212</v>
       </c>
       <c r="K28" t="n">
         <v>212</v>
@@ -29599,7 +29599,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>193.5578254626138</v>
       </c>
       <c r="N29" t="n">
         <v>212</v>
@@ -29666,31 +29666,31 @@
         <v>212</v>
       </c>
       <c r="I30" t="n">
+        <v>190.0216689102165</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.643407578228982</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>212</v>
       </c>
-      <c r="J30" t="n">
-        <v>204.8787205957731</v>
-      </c>
-      <c r="K30" t="n">
-        <v>13.97894284945579</v>
-      </c>
-      <c r="L30" t="n">
-        <v>120.0656026205451</v>
-      </c>
-      <c r="M30" t="n">
-        <v>185.2747782656032</v>
-      </c>
       <c r="N30" t="n">
-        <v>212</v>
+        <v>146.0325997042048</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>40.10796338750741</v>
       </c>
       <c r="P30" t="n">
         <v>132.1553865711792</v>
       </c>
       <c r="Q30" t="n">
-        <v>72.58809527915881</v>
+        <v>89.86329062269219</v>
       </c>
       <c r="R30" t="n">
         <v>212</v>
@@ -29748,7 +29748,7 @@
         <v>212</v>
       </c>
       <c r="J31" t="n">
-        <v>212</v>
+        <v>165.6069488359078</v>
       </c>
       <c r="K31" t="n">
         <v>212</v>
@@ -29836,7 +29836,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>83.69617113005324</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>119.6530747047185</v>
@@ -29903,10 +29903,10 @@
         <v>265</v>
       </c>
       <c r="I33" t="n">
-        <v>246.5981751483733</v>
+        <v>207.7492508027455</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>34.53213741945495</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -29918,7 +29918,7 @@
         <v>185.2747782656032</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>146.0325997042048</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>249.5880952791588</v>
+        <v>265.0000000000001</v>
       </c>
       <c r="R33" t="n">
         <v>265</v>
@@ -30061,7 +30061,7 @@
         <v>265</v>
       </c>
       <c r="I35" t="n">
-        <v>93.35667727062432</v>
+        <v>214.0036929944046</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30073,7 +30073,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>190.8467367395122</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -30085,7 +30085,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13.93270442798791</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>158.453483250405</v>
@@ -30140,22 +30140,22 @@
         <v>265</v>
       </c>
       <c r="I36" t="n">
-        <v>265</v>
+        <v>207.7492508027455</v>
       </c>
       <c r="J36" t="n">
         <v>27.87872059577307</v>
       </c>
       <c r="K36" t="n">
-        <v>101.6637777689183</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>120.0656026205451</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>249.5880952791588</v>
+        <v>159.7689909216388</v>
       </c>
       <c r="R36" t="n">
         <v>265</v>
@@ -30222,7 +30222,7 @@
         <v>265</v>
       </c>
       <c r="J37" t="n">
-        <v>226.8139382360957</v>
+        <v>265</v>
       </c>
       <c r="K37" t="n">
         <v>265</v>
@@ -30298,7 +30298,7 @@
         <v>265</v>
       </c>
       <c r="I38" t="n">
-        <v>93.35667727062432</v>
+        <v>214.0036929944046</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30310,10 +30310,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="N38" t="n">
-        <v>119.6530747047185</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>214.9692110349638</v>
+        <v>158.453483250405</v>
       </c>
       <c r="S38" t="n">
         <v>265</v>
@@ -30377,10 +30377,10 @@
         <v>265</v>
       </c>
       <c r="I39" t="n">
-        <v>190.0216689102165</v>
+        <v>249.359491958059</v>
       </c>
       <c r="J39" t="n">
-        <v>27.87872059577307</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -30392,7 +30392,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>249.5880952791588</v>
+        <v>89.86329062269219</v>
       </c>
       <c r="R39" t="n">
         <v>265</v>
@@ -30547,7 +30547,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7054865267859</v>
+        <v>54</v>
       </c>
       <c r="N41" t="n">
         <v>54</v>
@@ -30620,7 +30620,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -30632,7 +30632,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>54</v>
+        <v>13.57916810217353</v>
       </c>
       <c r="P42" t="n">
         <v>54</v>
@@ -30784,7 +30784,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>45.54271356783919</v>
+        <v>53</v>
       </c>
       <c r="N44" t="n">
         <v>53</v>
@@ -30796,7 +30796,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>13.93270442798791</v>
       </c>
       <c r="R44" t="n">
         <v>53</v>
@@ -30857,16 +30857,16 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>53</v>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>12.84331904556986</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -32528,7 +32528,7 @@
         <v>187.1621005025126</v>
       </c>
       <c r="L20" t="n">
-        <v>231.9999999999999</v>
+        <v>232</v>
       </c>
       <c r="M20" t="n">
         <v>258.3573768844221</v>
@@ -32765,7 +32765,7 @@
         <v>187.1621005025126</v>
       </c>
       <c r="L23" t="n">
-        <v>231.9999999999999</v>
+        <v>232</v>
       </c>
       <c r="M23" t="n">
         <v>258.3573768844221</v>
@@ -33485,7 +33485,7 @@
         <v>262.5378693467337</v>
       </c>
       <c r="O32" t="n">
-        <v>247.2478695740925</v>
+        <v>247.2478695740924</v>
       </c>
       <c r="P32" t="n">
         <v>177.2870600406814</v>
@@ -33959,7 +33959,7 @@
         <v>262.5378693467337</v>
       </c>
       <c r="O38" t="n">
-        <v>247.2478695740924</v>
+        <v>247.2478695740925</v>
       </c>
       <c r="P38" t="n">
         <v>177.2870600406814</v>
@@ -34433,7 +34433,7 @@
         <v>262.5378693467337</v>
       </c>
       <c r="O44" t="n">
-        <v>247.2478695740924</v>
+        <v>247.2478695740925</v>
       </c>
       <c r="P44" t="n">
         <v>177.2870600406814</v>
@@ -35451,7 +35451,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>12.99630700559545</v>
+        <v>20.67252009416694</v>
       </c>
       <c r="J11" t="n">
         <v>89.83656159410566</v>
@@ -35466,7 +35466,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.676213088571519</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>177.6591957525407</v>
@@ -35530,28 +35530,28 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>19.25074919725447</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>199.5860213320153</v>
       </c>
       <c r="K12" t="n">
-        <v>22.34646283438158</v>
+        <v>232</v>
       </c>
       <c r="L12" t="n">
-        <v>232</v>
+        <v>56.93439737945495</v>
       </c>
       <c r="M12" t="n">
-        <v>24.79959687948549</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>80.96740029579516</v>
+        <v>183.9551607695824</v>
       </c>
       <c r="O12" t="n">
-        <v>232</v>
+        <v>64.16936033908146</v>
       </c>
       <c r="P12" t="n">
-        <v>170.1253440420382</v>
+        <v>44.84461342882075</v>
       </c>
       <c r="Q12" t="n">
         <v>137.1367093773078</v>
@@ -35688,10 +35688,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>20.67252009416694</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>89.83656159410566</v>
+        <v>110.5090816882726</v>
       </c>
       <c r="K14" t="n">
         <v>187.1621005025126</v>
@@ -35767,31 +35767,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>37.97833108978354</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>200.1212794042269</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>22.34646283438158</v>
+        <v>232</v>
       </c>
       <c r="L15" t="n">
-        <v>56.93439737945495</v>
+        <v>232</v>
       </c>
       <c r="M15" t="n">
-        <v>118.8658227176446</v>
+        <v>232</v>
       </c>
       <c r="N15" t="n">
-        <v>81.96740029579516</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>200.1560507553141</v>
+        <v>46.08090234712569</v>
       </c>
       <c r="P15" t="n">
         <v>44.84461342882075</v>
       </c>
       <c r="Q15" t="n">
-        <v>155.4119047208412</v>
+        <v>131.7007468503161</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35940,7 +35940,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>20.67252009416706</v>
       </c>
       <c r="O17" t="n">
         <v>177.6591957525407</v>
@@ -35952,7 +35952,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>20.67252009416718</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -36004,16 +36004,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>37.97833108978354</v>
+        <v>20.25074919725446</v>
       </c>
       <c r="J18" t="n">
-        <v>200.1212794042269</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>22.34646283438158</v>
       </c>
       <c r="L18" t="n">
-        <v>56.93439737945495</v>
+        <v>232</v>
       </c>
       <c r="M18" t="n">
         <v>42.72522173439683</v>
@@ -36022,13 +36022,13 @@
         <v>81.96740029579516</v>
       </c>
       <c r="O18" t="n">
-        <v>232</v>
+        <v>131.9245238435935</v>
       </c>
       <c r="P18" t="n">
         <v>232</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.55316988822369</v>
+        <v>155.4119047208412</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36080,10 +36080,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.096873898381384</v>
+        <v>5.096873898381375</v>
       </c>
       <c r="I19" t="n">
-        <v>71.21454437988173</v>
+        <v>71.21454437988174</v>
       </c>
       <c r="J19" t="n">
         <v>232</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>20.79543349374229</v>
+        <v>20.79543349374228</v>
       </c>
       <c r="U19" t="n">
         <v>77.07760872554206</v>
@@ -36162,16 +36162,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>13.99630700559545</v>
       </c>
       <c r="J20" t="n">
-        <v>89.83656159410566</v>
+        <v>96.51277468267713</v>
       </c>
       <c r="K20" t="n">
-        <v>187.1621005025125</v>
+        <v>187.1621005025126</v>
       </c>
       <c r="L20" t="n">
-        <v>231.9999999999999</v>
+        <v>232</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -36189,7 +36189,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>20.67252009416718</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36241,10 +36241,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>37.97833108978354</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>145.6981366783282</v>
+        <v>232</v>
       </c>
       <c r="K21" t="n">
         <v>232</v>
@@ -36256,16 +36256,16 @@
         <v>42.72522173439683</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>183.7948365330905</v>
       </c>
       <c r="O21" t="n">
         <v>46.08090234712569</v>
       </c>
       <c r="P21" t="n">
-        <v>201.7973686763322</v>
+        <v>44.84461342882075</v>
       </c>
       <c r="Q21" t="n">
-        <v>155.4119047208412</v>
+        <v>80.24629120337369</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>89.83656159410566</v>
+        <v>110.5090816882726</v>
       </c>
       <c r="K23" t="n">
-        <v>187.1621005025125</v>
+        <v>187.1621005025126</v>
       </c>
       <c r="L23" t="n">
-        <v>231.9999999999999</v>
+        <v>232</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -36423,7 +36423,7 @@
         <v>211.2958846829367</v>
       </c>
       <c r="Q23" t="n">
-        <v>20.67252009416718</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36484,11 +36484,11 @@
         <v>200.1212794042269</v>
       </c>
       <c r="K24" t="n">
+        <v>22.34646283438158</v>
+      </c>
+      <c r="L24" t="n">
         <v>232</v>
       </c>
-      <c r="L24" t="n">
-        <v>56.93439737945495</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -36496,13 +36496,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>46.08090234712569</v>
+        <v>220.035551679047</v>
       </c>
       <c r="P24" t="n">
-        <v>232</v>
+        <v>85.73551013404477</v>
       </c>
       <c r="Q24" t="n">
-        <v>131.2389342982006</v>
+        <v>138.1367093773078</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36715,16 +36715,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>21.97833108978354</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>129.9866845014766</v>
       </c>
       <c r="K27" t="n">
         <v>177</v>
       </c>
       <c r="L27" t="n">
-        <v>166.1479347652123</v>
+        <v>172.0171869181874</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -36736,7 +36736,7 @@
         <v>177</v>
       </c>
       <c r="P27" t="n">
-        <v>158.7222189934889</v>
+        <v>44.84461342882075</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36952,25 +36952,25 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>21.47477652172662</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>177</v>
       </c>
       <c r="K30" t="n">
-        <v>36.32540568383737</v>
+        <v>177</v>
       </c>
       <c r="L30" t="n">
-        <v>177</v>
+        <v>56.93439737945495</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>26.72522173439683</v>
       </c>
       <c r="N30" t="n">
-        <v>65.96740029579516</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>46.08090234712569</v>
+        <v>86.18886573463308</v>
       </c>
       <c r="P30" t="n">
         <v>177</v>
@@ -37031,7 +37031,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>55.21454437988173</v>
+        <v>55.21454437988174</v>
       </c>
       <c r="J31" t="n">
         <v>177</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>4.795433493742285</v>
+        <v>4.79543349374228</v>
       </c>
       <c r="U31" t="n">
         <v>61.07760872554206</v>
@@ -37189,31 +37189,31 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>56.57650623815683</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>6.653416823681882</v>
       </c>
       <c r="K33" t="n">
-        <v>22.34646283438158</v>
+        <v>177</v>
       </c>
       <c r="L33" t="n">
+        <v>120.2137452186744</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>177</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>177</v>
-      </c>
-      <c r="O33" t="n">
-        <v>46.08090234712569</v>
       </c>
       <c r="P33" t="n">
         <v>44.84461342882075</v>
       </c>
       <c r="Q33" t="n">
-        <v>177</v>
+        <v>175.1367093773079</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37426,31 +37426,31 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>74.97833108978354</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>124.0102406032999</v>
+        <v>22.34646283438158</v>
       </c>
       <c r="L36" t="n">
-        <v>56.93439737945495</v>
+        <v>177</v>
       </c>
       <c r="M36" t="n">
         <v>177</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>118.9674002957952</v>
       </c>
       <c r="O36" t="n">
         <v>46.08090234712569</v>
       </c>
       <c r="P36" t="n">
-        <v>44.84461342882075</v>
+        <v>89.5480190722355</v>
       </c>
       <c r="Q36" t="n">
-        <v>177</v>
+        <v>69.90570029894666</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37499,7 +37499,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>20.61612715846996</v>
+        <v>20.61612715846997</v>
       </c>
       <c r="H37" t="n">
         <v>42.09687389838138</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>57.79543349374228</v>
+        <v>57.79543349374229</v>
       </c>
       <c r="U37" t="n">
         <v>114.0776087255421</v>
@@ -37663,31 +37663,31 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>59.33782304784256</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>80.02117139728833</v>
+        <v>22.34646283438158</v>
       </c>
       <c r="L39" t="n">
-        <v>56.93439737945495</v>
+        <v>177</v>
       </c>
       <c r="M39" t="n">
         <v>177</v>
       </c>
       <c r="N39" t="n">
-        <v>118.9674002957952</v>
+        <v>43.31958553743991</v>
       </c>
       <c r="O39" t="n">
-        <v>46.08090234712569</v>
+        <v>177</v>
       </c>
       <c r="P39" t="n">
         <v>44.84461342882075</v>
       </c>
       <c r="Q39" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37906,19 +37906,19 @@
         <v>177</v>
       </c>
       <c r="K42" t="n">
-        <v>76.34646283438158</v>
+        <v>22.34646283438158</v>
       </c>
       <c r="L42" t="n">
         <v>56.93439737945495</v>
       </c>
       <c r="M42" t="n">
+        <v>109.0629407565284</v>
+      </c>
+      <c r="N42" t="n">
         <v>177</v>
       </c>
-      <c r="N42" t="n">
-        <v>14.64210885870198</v>
-      </c>
       <c r="O42" t="n">
-        <v>100.0809023471257</v>
+        <v>59.66007044929921</v>
       </c>
       <c r="P42" t="n">
         <v>98.84461342882075</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="K45" t="n">
-        <v>177</v>
+        <v>22.34646283438158</v>
       </c>
       <c r="L45" t="n">
-        <v>56.93439737945495</v>
+        <v>109.9343973794549</v>
       </c>
       <c r="M45" t="n">
-        <v>177</v>
+        <v>168.4867222875226</v>
       </c>
       <c r="N45" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>46.08090234712569</v>
       </c>
       <c r="P45" t="n">
-        <v>66.83318512190421</v>
+        <v>177</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
